--- a/src/attributions/attributions_saliency_traj_94.xlsx
+++ b/src/attributions/attributions_saliency_traj_94.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9.762870831764303e-06</v>
+        <v>0.04746681451797485</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001317854766966775</v>
+        <v>0.4080151915550232</v>
       </c>
       <c r="C3" t="n">
-        <v>2.842604590114206e-05</v>
+        <v>0.1269989609718323</v>
       </c>
       <c r="D3" t="n">
-        <v>8.784600504441187e-05</v>
+        <v>0.04059894010424614</v>
       </c>
       <c r="E3" t="n">
-        <v>9.979306923924014e-06</v>
+        <v>0.07744257152080536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001766437198966742</v>
+        <v>0.1295735388994217</v>
       </c>
       <c r="G3" t="n">
-        <v>3.542667400324717e-05</v>
+        <v>0.01053673774003983</v>
       </c>
       <c r="H3" t="n">
-        <v>6.80671219015494e-05</v>
+        <v>0.007130276411771774</v>
       </c>
       <c r="I3" t="n">
-        <v>1.344442171102855e-05</v>
+        <v>0.09911797940731049</v>
       </c>
       <c r="J3" t="n">
-        <v>4.461725256987847e-05</v>
+        <v>0.05391509458422661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001108707147068344</v>
+        <v>0.5600674152374268</v>
       </c>
       <c r="L3" t="n">
-        <v>3.440705768298358e-05</v>
+        <v>0.08479113131761551</v>
       </c>
       <c r="M3" t="n">
-        <v>6.19334532530047e-05</v>
+        <v>0.0913570374250412</v>
       </c>
       <c r="N3" t="n">
-        <v>6.910721276653931e-05</v>
+        <v>0.167079359292984</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001094831095542759</v>
+        <v>0.06094253435730934</v>
       </c>
       <c r="P3" t="n">
-        <v>3.868241037707776e-05</v>
+        <v>0.04238434880971909</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.092319118673913e-05</v>
+        <v>0.1201785653829575</v>
       </c>
       <c r="R3" t="n">
-        <v>2.286826429553912e-06</v>
+        <v>0.04447010159492493</v>
       </c>
       <c r="S3" t="n">
-        <v>6.882347861392191e-06</v>
+        <v>0.002374268136918545</v>
       </c>
       <c r="T3" t="n">
-        <v>1.581782271387056e-06</v>
+        <v>0.07863710820674896</v>
       </c>
       <c r="U3" t="n">
-        <v>2.493016654625535e-05</v>
+        <v>0.005780123174190521</v>
       </c>
       <c r="V3" t="n">
-        <v>4.948048172082053e-06</v>
+        <v>0.1205145865678787</v>
       </c>
       <c r="W3" t="n">
-        <v>3.846260369755328e-05</v>
+        <v>0.01671823300421238</v>
       </c>
       <c r="X3" t="n">
-        <v>3.112652120762505e-05</v>
+        <v>0.05717001855373383</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.107593875029124e-05</v>
+        <v>0.009708419442176819</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.784352990507614e-06</v>
+        <v>0.05624347552657127</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.70269286679104e-06</v>
+        <v>0.05868412554264069</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.716197923291475e-05</v>
+        <v>0.0518118292093277</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.268150390387746e-05</v>
+        <v>0.05143100023269653</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.771247793338262e-05</v>
+        <v>0.07087340950965881</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.582677916507237e-05</v>
+        <v>0.09667675197124481</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.300220901612192e-06</v>
+        <v>0.1465398669242859</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.281348249904113e-05</v>
+        <v>0.05880049243569374</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.158465420303401e-05</v>
+        <v>0.002114592352882028</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.130521170329303e-05</v>
+        <v>0.1434840559959412</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.079793557641096e-05</v>
+        <v>0.01803353987634182</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.980840534088202e-05</v>
+        <v>0.02090714313089848</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.514840914751403e-05</v>
+        <v>0.1818141788244247</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.853637513704598e-05</v>
+        <v>0.06830963492393494</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.526492597913602e-06</v>
+        <v>0.02401155419647694</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.117222513537854e-05</v>
+        <v>0.1260360479354858</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.02121149818413e-05</v>
+        <v>0.04698498547077179</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.575109126861207e-05</v>
+        <v>0.04081204533576965</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.873843550332822e-05</v>
+        <v>0.02747762948274612</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.453444024780765e-06</v>
+        <v>0.06419151276350021</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.618605534138624e-06</v>
+        <v>0.0285115260630846</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.726010203943588e-05</v>
+        <v>0.4843666553497314</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.777808731480036e-05</v>
+        <v>0.01591514609754086</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.471739157452248e-05</v>
+        <v>0.006916929967701435</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.929467857233249e-05</v>
+        <v>0.06476037204265594</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0001195798395201564</v>
+        <v>0.09895021468400955</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.966227450291626e-05</v>
+        <v>0.04200368374586105</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.690560333780013e-06</v>
+        <v>0.07611104100942612</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.953539140231442e-05</v>
+        <v>0.06287052482366562</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.240952643565834e-09</v>
+        <v>0.01009738259017467</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.518252146430314e-05</v>
+        <v>0.2383990734815598</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.645097634347621e-06</v>
+        <v>0.06496688723564148</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.653777871979401e-05</v>
+        <v>0.04776992648839951</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.054931635735556e-05</v>
+        <v>0.1102648824453354</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.691141374583822e-06</v>
+        <v>0.02436300925910473</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.173762823076686e-06</v>
+        <v>0.0756836012005806</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3.716726268976345e-06</v>
+        <v>0.001093432772904634</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.916580913530197e-06</v>
+        <v>0.0411173403263092</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.387804124737158e-05</v>
+        <v>0.06185524165630341</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.046831104962621e-05</v>
+        <v>0.01793636381626129</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.958169559657108e-05</v>
+        <v>0.007621424272656441</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.083287836285308e-05</v>
+        <v>0.03267508372664452</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.758878508757334e-06</v>
+        <v>0.01215708907693624</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.524013987364015e-05</v>
+        <v>0.0404568538069725</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.133922887674998e-05</v>
+        <v>0.1569483876228333</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.067108496499714e-05</v>
+        <v>0.04159129410982132</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.605167926754802e-05</v>
+        <v>0.04104313254356384</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.181241441372549e-05</v>
+        <v>0.009984470903873444</v>
       </c>
       <c r="BV3" t="n">
-        <v>3.659652793430723e-05</v>
+        <v>0.2932379543781281</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.863516627054196e-05</v>
+        <v>0.05843513458967209</v>
       </c>
       <c r="BX3" t="n">
-        <v>3.337743692100048e-05</v>
+        <v>0.08222195506095886</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.204963064083131e-05</v>
+        <v>0.01696582697331905</v>
       </c>
       <c r="BZ3" t="n">
-        <v>6.700855738017708e-05</v>
+        <v>0.09416376054286957</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.500085454608779e-05</v>
+        <v>0.04670007899403572</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.062029787135543e-05</v>
+        <v>0.04164871573448181</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.512087449867977e-07</v>
+        <v>0.05142622441053391</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.281519689655397e-05</v>
+        <v>0.002462615026161075</v>
       </c>
       <c r="CE3" t="n">
-        <v>9.708906873129308e-06</v>
+        <v>0.1633929908275604</v>
       </c>
       <c r="CF3" t="n">
-        <v>4.814425210497575e-06</v>
+        <v>0.01067289616912603</v>
       </c>
       <c r="CG3" t="n">
-        <v>8.787019396550022e-06</v>
+        <v>0.02476748265326023</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.325051380263176e-05</v>
+        <v>0.001600203337147832</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.637808938743547e-05</v>
+        <v>0.04835944622755051</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.14125414256705e-05</v>
+        <v>0.03087233379483223</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.755705307004973e-05</v>
+        <v>0.01476655527949333</v>
       </c>
       <c r="CL3" t="n">
-        <v>4.534151685220422e-07</v>
+        <v>0.009393169544637203</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.34290057758335e-05</v>
+        <v>0.06619562953710556</v>
       </c>
       <c r="CN3" t="n">
-        <v>4.482988970266888e-06</v>
+        <v>0.1655618250370026</v>
       </c>
       <c r="CO3" t="n">
-        <v>9.229817806044593e-06</v>
+        <v>0.04377375543117523</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.886069367174059e-05</v>
+        <v>0.0538148358464241</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.517796590633225e-05</v>
+        <v>0.0920833945274353</v>
       </c>
       <c r="CR3" t="n">
-        <v>7.040458513074555e-06</v>
+        <v>0.04400536045432091</v>
       </c>
       <c r="CS3" t="n">
-        <v>1.449127921659965e-06</v>
+        <v>0.04686623439192772</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.816340565914288e-05</v>
+        <v>0.008383849635720253</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.694341517577413e-05</v>
+        <v>0.008338809013366699</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.854832124896348e-06</v>
+        <v>0.01931007765233517</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.529245309939142e-05</v>
+        <v>0.1625530272722244</v>
       </c>
       <c r="CX3" t="n">
-        <v>3.192637905158335e-06</v>
+        <v>0.0160752646625042</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.176734258478973e-05</v>
+        <v>0.008419495075941086</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.002883095679863e-06</v>
+        <v>0.0001548894215375185</v>
       </c>
       <c r="DA3" t="n">
-        <v>3.081349495914765e-05</v>
+        <v>0.06132513657212257</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.708306965359952e-06</v>
+        <v>0.01524074282497168</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.678675082279369e-05</v>
+        <v>0.01255285739898682</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.467037797439843e-07</v>
+        <v>0.009210124611854553</v>
       </c>
       <c r="DE3" t="n">
-        <v>2.710662738536485e-05</v>
+        <v>0.07985834777355194</v>
       </c>
       <c r="DF3" t="n">
-        <v>3.140991611871868e-05</v>
+        <v>0.04515055194497108</v>
       </c>
       <c r="DG3" t="n">
-        <v>7.161088888096856e-06</v>
+        <v>0.04248060658574104</v>
       </c>
       <c r="DH3" t="n">
-        <v>4.085912951268256e-05</v>
+        <v>0.0202275924384594</v>
       </c>
       <c r="DI3" t="n">
-        <v>3.608786209952086e-05</v>
+        <v>0.1117953062057495</v>
       </c>
       <c r="DJ3" t="n">
-        <v>8.021615940378979e-07</v>
+        <v>0.07094621658325195</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.447070412221365e-06</v>
+        <v>0.03210480138659477</v>
       </c>
       <c r="DL3" t="n">
-        <v>6.394973024725914e-05</v>
+        <v>0.009243990294635296</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.615247856534552e-05</v>
+        <v>0.015671506524086</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.62069463840453e-05</v>
+        <v>0.03656407818198204</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.876755777630024e-05</v>
+        <v>0.04958920925855637</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.393094655417372e-05</v>
+        <v>0.01537447795271873</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.468960181227885e-05</v>
+        <v>0.05943290144205093</v>
       </c>
       <c r="DR3" t="n">
-        <v>2.419470365566667e-05</v>
+        <v>0.001894580200314522</v>
       </c>
       <c r="DS3" t="n">
-        <v>2.33516175285331e-06</v>
+        <v>0.02858182042837143</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.622571289772168e-05</v>
+        <v>0.02357938326895237</v>
       </c>
       <c r="DU3" t="n">
-        <v>1.262134901480749e-05</v>
+        <v>0.06993571668863297</v>
       </c>
       <c r="DV3" t="n">
-        <v>1.701142195997818e-06</v>
+        <v>0.03622210398316383</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.499128186173039e-06</v>
+        <v>0.04443251341581345</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.152478014584631e-06</v>
+        <v>0.1084547340869904</v>
       </c>
       <c r="DY3" t="n">
-        <v>2.047751422651345e-06</v>
+        <v>0.01340613514184952</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.27605775964912e-05</v>
+        <v>0.03064042516052723</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.983037873287685e-05</v>
+        <v>0.03640007972717285</v>
       </c>
       <c r="EB3" t="n">
-        <v>9.377610695082694e-06</v>
+        <v>0.170327216386795</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.026396603265312e-06</v>
+        <v>0.009563338942825794</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.953804166987538e-05</v>
+        <v>0.03924112394452095</v>
       </c>
       <c r="EE3" t="n">
-        <v>4.802575858775526e-06</v>
+        <v>0.003210194408893585</v>
       </c>
       <c r="EF3" t="n">
-        <v>4.017804712930229e-06</v>
+        <v>0.01475403178483248</v>
       </c>
       <c r="EG3" t="n">
-        <v>1.267588572773093e-06</v>
+        <v>0.0774465948343277</v>
       </c>
       <c r="EH3" t="n">
-        <v>1.589036037330516e-05</v>
+        <v>0.009999566711485386</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.598787207512942e-06</v>
+        <v>0.08780535310506821</v>
       </c>
       <c r="EJ3" t="n">
-        <v>3.799274963967036e-06</v>
+        <v>0.0008271256228908896</v>
       </c>
       <c r="EK3" t="n">
-        <v>3.352627390995622e-05</v>
+        <v>0.004273887723684311</v>
       </c>
       <c r="EL3" t="n">
-        <v>1.099244218494277e-05</v>
+        <v>0.004148390144109726</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.390033503412269e-05</v>
+        <v>0.01609093323349953</v>
       </c>
       <c r="EN3" t="n">
-        <v>7.544762866018573e-06</v>
+        <v>0.020938316360116</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.781936134648276e-06</v>
+        <v>0.02514862641692162</v>
       </c>
       <c r="EP3" t="n">
-        <v>4.53847997050616e-06</v>
+        <v>0.08852657675743103</v>
       </c>
       <c r="EQ3" t="n">
-        <v>2.601317191874841e-06</v>
+        <v>0.007249168120324612</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.473702377552399e-05</v>
+        <v>0.03464694693684578</v>
       </c>
       <c r="ES3" t="n">
-        <v>7.832468327251263e-07</v>
+        <v>0.02033530734479427</v>
       </c>
       <c r="ET3" t="n">
-        <v>2.852915349649265e-05</v>
+        <v>0.003547187661752105</v>
       </c>
       <c r="EU3" t="n">
-        <v>1.824210448830854e-05</v>
+        <v>0.04279942810535431</v>
       </c>
       <c r="EV3" t="n">
-        <v>5.18004599143751e-05</v>
+        <v>0.03966020047664642</v>
       </c>
       <c r="EW3" t="n">
-        <v>4.41850716015324e-06</v>
+        <v>0.01155103743076324</v>
       </c>
       <c r="EX3" t="n">
-        <v>7.415820618916769e-06</v>
+        <v>0.01491093821823597</v>
       </c>
       <c r="EY3" t="n">
-        <v>7.810699571564328e-06</v>
+        <v>0.1812234222888947</v>
       </c>
       <c r="EZ3" t="n">
-        <v>4.903858098259661e-06</v>
+        <v>0.00833588745445013</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.166510355687933e-05</v>
+        <v>0.01610986888408661</v>
       </c>
       <c r="FB3" t="n">
-        <v>5.539752237382345e-06</v>
+        <v>0.003147478681057692</v>
       </c>
       <c r="FC3" t="n">
-        <v>2.305727866769303e-05</v>
+        <v>0.04720169678330421</v>
       </c>
       <c r="FD3" t="n">
-        <v>1.450562740501482e-05</v>
+        <v>0.02956066653132439</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.993830665014684e-05</v>
+        <v>0.0207140427082777</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.873821358662099e-07</v>
+        <v>0.01661462336778641</v>
       </c>
       <c r="FG3" t="n">
-        <v>8.424481166002806e-07</v>
+        <v>0.03134956210851669</v>
       </c>
       <c r="FH3" t="n">
-        <v>2.476725967426319e-05</v>
+        <v>0.08801613748073578</v>
       </c>
       <c r="FI3" t="n">
-        <v>1.327933932770975e-05</v>
+        <v>0.06079714372754097</v>
       </c>
       <c r="FJ3" t="n">
-        <v>5.395506013883278e-05</v>
+        <v>0.07466422766447067</v>
       </c>
       <c r="FK3" t="n">
-        <v>6.892543751746416e-06</v>
+        <v>0.09432889521121979</v>
       </c>
       <c r="FL3" t="n">
-        <v>2.261832923977636e-05</v>
+        <v>0.03120240196585655</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.568785046401899e-05</v>
+        <v>0.04032851010560989</v>
       </c>
       <c r="FN3" t="n">
-        <v>8.790777428657748e-06</v>
+        <v>0.04328474402427673</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.393226011714432e-05</v>
+        <v>0.08255951106548309</v>
       </c>
       <c r="FP3" t="n">
-        <v>1.555785820528399e-05</v>
+        <v>0.1308691501617432</v>
       </c>
       <c r="FQ3" t="n">
-        <v>6.944179767742753e-05</v>
+        <v>0.1945638656616211</v>
       </c>
       <c r="FR3" t="n">
-        <v>1.671776590228546e-05</v>
+        <v>0.1133748516440392</v>
       </c>
       <c r="FS3" t="n">
-        <v>4.642758722184226e-05</v>
+        <v>0.1119671911001205</v>
       </c>
       <c r="FT3" t="n">
-        <v>2.997064802912064e-05</v>
+        <v>0.07230165600776672</v>
       </c>
       <c r="FU3" t="n">
-        <v>5.653285188600421e-05</v>
+        <v>0.1411179155111313</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.949810030055232e-05</v>
+        <v>0.007700088433921337</v>
       </c>
       <c r="FW3" t="n">
-        <v>1.248268654308049e-05</v>
+        <v>0.0317947156727314</v>
       </c>
       <c r="FX3" t="n">
-        <v>1.248617763849325e-06</v>
+        <v>0.0394870862364769</v>
       </c>
       <c r="FY3" t="n">
-        <v>1.451961361453868e-05</v>
+        <v>0.02509807609021664</v>
       </c>
       <c r="FZ3" t="n">
-        <v>5.648951173498062e-06</v>
+        <v>0.07208164036273956</v>
       </c>
       <c r="GA3" t="n">
-        <v>9.158016837318428e-06</v>
+        <v>0.08198602497577667</v>
       </c>
       <c r="GB3" t="n">
-        <v>9.990022590500303e-06</v>
+        <v>0.06540461629629135</v>
       </c>
       <c r="GC3" t="n">
-        <v>5.955812957836315e-05</v>
+        <v>0.01582568325102329</v>
       </c>
       <c r="GD3" t="n">
-        <v>1.567525941936765e-06</v>
+        <v>0.01066640857607126</v>
       </c>
       <c r="GE3" t="n">
-        <v>4.735699621960521e-05</v>
+        <v>0.02916157059371471</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.614276516193058e-05</v>
+        <v>0.06678424775600433</v>
       </c>
       <c r="GG3" t="n">
-        <v>7.09846517565893e-06</v>
+        <v>0.03726647049188614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4.51949283553077e-10</v>
+        <v>0.07241284102201462</v>
       </c>
       <c r="B4" t="n">
-        <v>6.114477257845863e-10</v>
+        <v>0.06073638424277306</v>
       </c>
       <c r="C4" t="n">
-        <v>4.243118634228438e-10</v>
+        <v>0.05308881774544716</v>
       </c>
       <c r="D4" t="n">
-        <v>2.053907044441416e-10</v>
+        <v>0.02782234363257885</v>
       </c>
       <c r="E4" t="n">
-        <v>3.381834812188345e-10</v>
+        <v>0.01744988188147545</v>
       </c>
       <c r="F4" t="n">
-        <v>1.686014661217428e-09</v>
+        <v>0.02751230821013451</v>
       </c>
       <c r="G4" t="n">
-        <v>1.088232143287016e-10</v>
+        <v>0.03012922406196594</v>
       </c>
       <c r="H4" t="n">
-        <v>8.970620357651171e-10</v>
+        <v>0.01231796108186245</v>
       </c>
       <c r="I4" t="n">
-        <v>7.466008367096322e-11</v>
+        <v>0.01673977077007294</v>
       </c>
       <c r="J4" t="n">
-        <v>1.282363382149043e-10</v>
+        <v>0.06741684675216675</v>
       </c>
       <c r="K4" t="n">
-        <v>5.202049901953387e-10</v>
+        <v>0.05290192365646362</v>
       </c>
       <c r="L4" t="n">
-        <v>3.106974399980089e-10</v>
+        <v>0.05233174562454224</v>
       </c>
       <c r="M4" t="n">
-        <v>3.498834832971198e-10</v>
+        <v>0.02325139753520489</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54152532352947e-11</v>
+        <v>0.04622826725244522</v>
       </c>
       <c r="O4" t="n">
-        <v>1.114035974580929e-09</v>
+        <v>0.04837755858898163</v>
       </c>
       <c r="P4" t="n">
-        <v>2.060704107353928e-10</v>
+        <v>0.02792878448963165</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.061838501800423e-10</v>
+        <v>0.006213866174221039</v>
       </c>
       <c r="R4" t="n">
-        <v>6.071320529654756e-11</v>
+        <v>0.01731845736503601</v>
       </c>
       <c r="S4" t="n">
-        <v>7.839139060106248e-11</v>
+        <v>0.0051770880818367</v>
       </c>
       <c r="T4" t="n">
-        <v>7.530505385933139e-11</v>
+        <v>0.02188942022621632</v>
       </c>
       <c r="U4" t="n">
-        <v>2.472235957617919e-11</v>
+        <v>0.00285640312358737</v>
       </c>
       <c r="V4" t="n">
-        <v>1.841488905807154e-10</v>
+        <v>0.02640538290143013</v>
       </c>
       <c r="W4" t="n">
-        <v>3.812269389058542e-10</v>
+        <v>0.03501324355602264</v>
       </c>
       <c r="X4" t="n">
-        <v>3.356909750173998e-10</v>
+        <v>0.01065334305167198</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.198301775670821e-11</v>
+        <v>0.006835158914327621</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67024227781809e-10</v>
+        <v>0.02604928240180016</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.549655345329143e-11</v>
+        <v>0.01267257146537304</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.857879211060066e-10</v>
+        <v>0.03797972202301025</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.895225504311426e-10</v>
+        <v>0.003824291750788689</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.696690176191453e-10</v>
+        <v>0.01669211499392986</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.622489890859782e-10</v>
+        <v>0.0003988612443208694</v>
       </c>
       <c r="AF4" t="n">
-        <v>5.820138815337828e-11</v>
+        <v>0.02221850678324699</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.179445707766291e-10</v>
+        <v>0.02034870535135269</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33857577799823e-10</v>
+        <v>0.02006120420992374</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.74661454375314e-12</v>
+        <v>0.001327797072008252</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.010565047783075e-10</v>
+        <v>0.01392029877752066</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.292458085000447e-10</v>
+        <v>0.03717643767595291</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.075135536154903e-10</v>
+        <v>0.005049468483775854</v>
       </c>
       <c r="AM4" t="n">
-        <v>9.508709791772318e-11</v>
+        <v>0.01030793040990829</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.189810998145305e-11</v>
+        <v>0.01036211103200912</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.817290207206668e-10</v>
+        <v>0.006703001447021961</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.104347972599953e-10</v>
+        <v>0.01141208317130804</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.270857308277584e-10</v>
+        <v>0.02311055921018124</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.424122510675147e-12</v>
+        <v>0.002552551217377186</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.664379606358679e-10</v>
+        <v>0.007708704099059105</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.95888535895017e-10</v>
+        <v>0.003936722874641418</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.030034166964015e-10</v>
+        <v>0.0177906695753336</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.997893600031887e-10</v>
+        <v>0.0492858961224556</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.474196958424102e-10</v>
+        <v>0.000149119645357132</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.559969399968281e-10</v>
+        <v>0.02513151057064533</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.207363653499272e-09</v>
+        <v>0.07950517535209656</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.834511709208897e-10</v>
+        <v>0.002908894326537848</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.215181371667541e-10</v>
+        <v>0.0184266772121191</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.522660024264269e-10</v>
+        <v>0.01350460294634104</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.8178318012273e-10</v>
+        <v>0.004343170672655106</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.405630694646277e-10</v>
+        <v>0.07128552347421646</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.685016792236539e-11</v>
+        <v>0.01145622506737709</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.329100133926289e-10</v>
+        <v>0.01130059268325567</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.377761515986009e-10</v>
+        <v>0.01293979585170746</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.435730783734158e-10</v>
+        <v>0.06808816641569138</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.386355474863876e-10</v>
+        <v>0.03946303203701973</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2.214376321196809e-10</v>
+        <v>0.0242720115929842</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.967693313316033e-10</v>
+        <v>0.0163879282772541</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.153328431704239e-10</v>
+        <v>0.05399998649954796</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.450964431410796e-10</v>
+        <v>0.00328346504829824</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.606576426395947e-10</v>
+        <v>0.02021347731351852</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.489187328480469e-11</v>
+        <v>0.002635269891470671</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.532948017996972e-10</v>
+        <v>0.0116099426522851</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.882928783533913e-11</v>
+        <v>0.0006465793703682721</v>
       </c>
       <c r="BR4" t="n">
-        <v>2.288852440912592e-11</v>
+        <v>0.005052604246884584</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.540843091480838e-10</v>
+        <v>0.005455754231661558</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.693527428350052e-11</v>
+        <v>0.01981091871857643</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.585952896787646e-10</v>
+        <v>0.01183184888213873</v>
       </c>
       <c r="BV4" t="n">
-        <v>2.127333031953782e-12</v>
+        <v>0.01482829451560974</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.757362890410292e-11</v>
+        <v>0.02832786552608013</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.336126001505455e-11</v>
+        <v>0.003972265869379044</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.872254821819411e-10</v>
+        <v>0.03083254583179951</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.195056217490503e-10</v>
+        <v>0.006138923112303019</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.82742795790314e-11</v>
+        <v>0.02611662447452545</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.096498890631239e-10</v>
+        <v>0.009365212172269821</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.168460021602982e-11</v>
+        <v>0.001463198568671942</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.364586050029708e-13</v>
+        <v>0.07384231686592102</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.614010869399607e-10</v>
+        <v>0.0006000455468893051</v>
       </c>
       <c r="CF4" t="n">
-        <v>5.907779820901737e-11</v>
+        <v>0.02605748176574707</v>
       </c>
       <c r="CG4" t="n">
-        <v>8.492501146761811e-11</v>
+        <v>0.008237346075475216</v>
       </c>
       <c r="CH4" t="n">
-        <v>9.550893409482342e-11</v>
+        <v>0.001834482420235872</v>
       </c>
       <c r="CI4" t="n">
-        <v>3.075500965010747e-10</v>
+        <v>0.002742520766332746</v>
       </c>
       <c r="CJ4" t="n">
-        <v>9.893488112089344e-11</v>
+        <v>0.003500225022435188</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.584632425277732e-10</v>
+        <v>0.00716291181743145</v>
       </c>
       <c r="CL4" t="n">
-        <v>5.170742306548348e-12</v>
+        <v>0.009310772642493248</v>
       </c>
       <c r="CM4" t="n">
-        <v>4.776970485842469e-12</v>
+        <v>0.05787111073732376</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.704352852767045e-10</v>
+        <v>0.01746533811092377</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.490281229121209e-11</v>
+        <v>0.05353651940822601</v>
       </c>
       <c r="CP4" t="n">
-        <v>4.723134106043858e-10</v>
+        <v>0.01508285850286484</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.136031434536335e-10</v>
+        <v>0.06203282624483109</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.417792632769533e-10</v>
+        <v>0.02673793211579323</v>
       </c>
       <c r="CS4" t="n">
-        <v>1.532703824969062e-10</v>
+        <v>0.00284082442522049</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.201485022583881e-10</v>
+        <v>0.06351666152477264</v>
       </c>
       <c r="CU4" t="n">
-        <v>2.491296058337866e-10</v>
+        <v>0.02984543517231941</v>
       </c>
       <c r="CV4" t="n">
-        <v>4.789368554525275e-11</v>
+        <v>0.07710563391447067</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.874861516037996e-10</v>
+        <v>0.002067715860903263</v>
       </c>
       <c r="CX4" t="n">
-        <v>5.198159264141466e-11</v>
+        <v>0.01742066442966461</v>
       </c>
       <c r="CY4" t="n">
-        <v>4.777808357281366e-11</v>
+        <v>0.007601636461913586</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.151402749868026e-13</v>
+        <v>0.00211922382004559</v>
       </c>
       <c r="DA4" t="n">
-        <v>3.406456228205457e-10</v>
+        <v>0.002416900126263499</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.103709901251193e-10</v>
+        <v>0.007373759523034096</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.355511341534111e-10</v>
+        <v>0.002598062390461564</v>
       </c>
       <c r="DD4" t="n">
-        <v>6.477700320584034e-11</v>
+        <v>0.01074588391929865</v>
       </c>
       <c r="DE4" t="n">
-        <v>5.743891473564133e-12</v>
+        <v>0.07820253074169159</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.105887395547178e-10</v>
+        <v>0.05581232160329819</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.99519178956109e-10</v>
+        <v>0.008614863269031048</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.545976485190948e-10</v>
+        <v>0.02461270056664944</v>
       </c>
       <c r="DI4" t="n">
-        <v>5.90731963345803e-10</v>
+        <v>0.04166334867477417</v>
       </c>
       <c r="DJ4" t="n">
-        <v>5.811380543452316e-11</v>
+        <v>0.01173471100628376</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.839602775666194e-10</v>
+        <v>0.02316203899681568</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.816340576889843e-10</v>
+        <v>0.01126745063811541</v>
       </c>
       <c r="DM4" t="n">
-        <v>5.213103906887007e-11</v>
+        <v>0.03377080708742142</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.158033807735492e-10</v>
+        <v>0.04627859592437744</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.260498927457832e-10</v>
+        <v>0.005244993604719639</v>
       </c>
       <c r="DP4" t="n">
-        <v>2.524568054607101e-10</v>
+        <v>0.05596354976296425</v>
       </c>
       <c r="DQ4" t="n">
-        <v>3.682515403724551e-11</v>
+        <v>0.02223721705377102</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.535811755548622e-10</v>
+        <v>0.03049619682133198</v>
       </c>
       <c r="DS4" t="n">
-        <v>1.078405004184546e-10</v>
+        <v>0.01692966371774673</v>
       </c>
       <c r="DT4" t="n">
-        <v>3.324576725027839e-11</v>
+        <v>0.03736446425318718</v>
       </c>
       <c r="DU4" t="n">
-        <v>9.363769482018114e-11</v>
+        <v>0.005760845728218555</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.064942661306191e-11</v>
+        <v>0.0131067493930459</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.50164339296488e-10</v>
+        <v>0.005392408929765224</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.767251206485909e-10</v>
+        <v>0.02635852992534637</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.194677855589134e-10</v>
+        <v>0.006922264583408833</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.770302793246969e-10</v>
+        <v>0.05432131886482239</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.840604335612284e-10</v>
+        <v>0.07945515960454941</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.606100252793397e-10</v>
+        <v>0.007950657047331333</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.241580879247529e-11</v>
+        <v>0.01177382655441761</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.824647377635102e-10</v>
+        <v>0.03182704374194145</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.18616644284586e-11</v>
+        <v>0.005054031498730183</v>
       </c>
       <c r="EF4" t="n">
-        <v>6.983335784638278e-12</v>
+        <v>0.06119251623749733</v>
       </c>
       <c r="EG4" t="n">
-        <v>1.81918119457336e-10</v>
+        <v>0.002603975124657154</v>
       </c>
       <c r="EH4" t="n">
-        <v>3.251876892762517e-11</v>
+        <v>0.0008193664252758026</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.280376082934964e-10</v>
+        <v>0.02792799472808838</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.799850130046465e-10</v>
+        <v>0.005709432996809483</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.946729444313178e-10</v>
+        <v>0.01367280445992947</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.281580397360926e-11</v>
+        <v>0.0009342692792415619</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.844132485606664e-11</v>
+        <v>0.0008142045699059963</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.438752866844695e-10</v>
+        <v>0.01470585726201534</v>
       </c>
       <c r="EO4" t="n">
-        <v>1.482292483201419e-10</v>
+        <v>0.04550298303365707</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.950461056028253e-11</v>
+        <v>0.02617762051522732</v>
       </c>
       <c r="EQ4" t="n">
-        <v>2.008926011654033e-11</v>
+        <v>0.01711694151163101</v>
       </c>
       <c r="ER4" t="n">
-        <v>4.876678921794664e-11</v>
+        <v>0.02894505299627781</v>
       </c>
       <c r="ES4" t="n">
-        <v>5.118204124410219e-11</v>
+        <v>0.01685163006186485</v>
       </c>
       <c r="ET4" t="n">
-        <v>3.439601936605641e-10</v>
+        <v>0.01714444905519485</v>
       </c>
       <c r="EU4" t="n">
-        <v>1.688091333384989e-10</v>
+        <v>0.003458489663898945</v>
       </c>
       <c r="EV4" t="n">
-        <v>2.957083466981203e-10</v>
+        <v>0.02822148613631725</v>
       </c>
       <c r="EW4" t="n">
-        <v>2.343084060107969e-11</v>
+        <v>0.04043609276413918</v>
       </c>
       <c r="EX4" t="n">
-        <v>4.677147558140859e-11</v>
+        <v>0.07570399343967438</v>
       </c>
       <c r="EY4" t="n">
-        <v>1.641120017659148e-10</v>
+        <v>0.004697890020906925</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.282480233122385e-10</v>
+        <v>0.01853949204087257</v>
       </c>
       <c r="FA4" t="n">
-        <v>5.999219176988646e-11</v>
+        <v>0.009383800439536572</v>
       </c>
       <c r="FB4" t="n">
-        <v>5.125659618965273e-11</v>
+        <v>0.02147144079208374</v>
       </c>
       <c r="FC4" t="n">
-        <v>2.863345116566052e-10</v>
+        <v>0.004000104032456875</v>
       </c>
       <c r="FD4" t="n">
-        <v>5.888803333853332e-11</v>
+        <v>0.003304207697510719</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.215117256287868e-10</v>
+        <v>0.003864266909658909</v>
       </c>
       <c r="FF4" t="n">
-        <v>9.37633581887809e-11</v>
+        <v>0.007818195968866348</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.077163774843015e-10</v>
+        <v>0.06353586912155151</v>
       </c>
       <c r="FH4" t="n">
-        <v>3.666353609599327e-10</v>
+        <v>0.02658161148428917</v>
       </c>
       <c r="FI4" t="n">
-        <v>2.239807783688263e-10</v>
+        <v>0.008311225101351738</v>
       </c>
       <c r="FJ4" t="n">
-        <v>2.25941890197312e-10</v>
+        <v>0.03020073287189007</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.964360202277859e-10</v>
+        <v>0.04913899302482605</v>
       </c>
       <c r="FL4" t="n">
-        <v>3.052744168563493e-10</v>
+        <v>0.03288578614592552</v>
       </c>
       <c r="FM4" t="n">
-        <v>5.471802871914733e-11</v>
+        <v>0.04084351658821106</v>
       </c>
       <c r="FN4" t="n">
-        <v>3.983234575510863e-11</v>
+        <v>0.001828704262152314</v>
       </c>
       <c r="FO4" t="n">
-        <v>9.861499811192331e-11</v>
+        <v>0.01939864084124565</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.941318217291155e-10</v>
+        <v>0.02654399164021015</v>
       </c>
       <c r="FQ4" t="n">
-        <v>4.691723676231163e-10</v>
+        <v>0.06813683360815048</v>
       </c>
       <c r="FR4" t="n">
-        <v>2.360352018004885e-11</v>
+        <v>0.02076764777302742</v>
       </c>
       <c r="FS4" t="n">
-        <v>4.161097022503668e-10</v>
+        <v>0.08381505310535431</v>
       </c>
       <c r="FT4" t="n">
-        <v>8.862575257007066e-11</v>
+        <v>0.1657508015632629</v>
       </c>
       <c r="FU4" t="n">
-        <v>2.924599451503695e-10</v>
+        <v>0.08952036499977112</v>
       </c>
       <c r="FV4" t="n">
-        <v>1.579041758459354e-10</v>
+        <v>0.009549062699079514</v>
       </c>
       <c r="FW4" t="n">
-        <v>9.791877725318088e-11</v>
+        <v>0.02946559898555279</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.509157547876285e-11</v>
+        <v>0.0531938336789608</v>
       </c>
       <c r="FY4" t="n">
-        <v>1.243516262183775e-10</v>
+        <v>0.06299730390310287</v>
       </c>
       <c r="FZ4" t="n">
-        <v>5.178453846288456e-11</v>
+        <v>0.016853341832757</v>
       </c>
       <c r="GA4" t="n">
-        <v>8.668672030198721e-11</v>
+        <v>0.01848862878978252</v>
       </c>
       <c r="GB4" t="n">
-        <v>4.42525682764483e-10</v>
+        <v>0.003274169750511646</v>
       </c>
       <c r="GC4" t="n">
-        <v>7.076277341866444e-10</v>
+        <v>0.03735791519284248</v>
       </c>
       <c r="GD4" t="n">
-        <v>1.197964782928551e-10</v>
+        <v>0.03084644861519337</v>
       </c>
       <c r="GE4" t="n">
-        <v>3.296216077863789e-10</v>
+        <v>0.05836077034473419</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.166010898945302e-10</v>
+        <v>0.002649888163432479</v>
       </c>
       <c r="GG4" t="n">
-        <v>4.743024029085774e-11</v>
+        <v>0.007742836140096188</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.004759999457746744</v>
+        <v>0.02388297207653522</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003335506189614534</v>
+        <v>0.001282679615542293</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004408754408359528</v>
+        <v>0.1224273443222046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006509728264063597</v>
+        <v>0.1934435963630676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001580400858074427</v>
+        <v>0.0117979571223259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001843392732553184</v>
+        <v>0.01716650277376175</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0008231434039771557</v>
+        <v>0.05621529743075371</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004276882857084274</v>
+        <v>0.02126371301710606</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003317877708468586</v>
+        <v>0.01955296844244003</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006741644814610481</v>
+        <v>0.005979720968753099</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003851513378322124</v>
+        <v>0.01250072848051786</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003877477953210473</v>
+        <v>0.1142735481262207</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007252041716128588</v>
+        <v>0.2050712555646896</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002936890814453363</v>
+        <v>0.02360735461115837</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0004201369592919946</v>
+        <v>0.0270845964550972</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002185447374358773</v>
+        <v>0.004537854343652725</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004211364313960075</v>
+        <v>0.028668362647295</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001739077502861619</v>
+        <v>0.02516402676701546</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00218583969399333</v>
+        <v>0.006619975436478853</v>
       </c>
       <c r="T5" t="n">
-        <v>0.000542525143828243</v>
+        <v>0.03578417748212814</v>
       </c>
       <c r="U5" t="n">
-        <v>4.955709300702438e-06</v>
+        <v>0.01375090889632702</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0004540526424534619</v>
+        <v>0.02587744407355785</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003556862706318498</v>
+        <v>0.0126897506415844</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001055910717695951</v>
+        <v>0.07860306650400162</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.263429531827569e-05</v>
+        <v>0.01536669954657555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005029724910855293</v>
+        <v>0.007065372075885534</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.472238313406706e-05</v>
+        <v>0.00509722949936986</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001701652654446661</v>
+        <v>0.000827849842607975</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002906404202803969</v>
+        <v>0.007563384249806404</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001585738937137648</v>
+        <v>0.04655545949935913</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0007443995564244688</v>
+        <v>0.04621041566133499</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0003936200519092381</v>
+        <v>0.06441334635019302</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001371970982290804</v>
+        <v>0.01937795616686344</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.00046085289795883</v>
+        <v>0.03564091771841049</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003123739152215421</v>
+        <v>0.06904181838035583</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001007883460260928</v>
+        <v>0.02662385441362858</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001928254787344486</v>
+        <v>0.0201101042330265</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.001652489299885929</v>
+        <v>0.02198201976716518</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0003012449597008526</v>
+        <v>0.02097103372216225</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0005182345048524439</v>
+        <v>0.06114782392978668</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0002669175446499139</v>
+        <v>0.02179738320410252</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0007989360601641238</v>
+        <v>0.005396279972046614</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001313352375291288</v>
+        <v>0.02316636964678764</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001046167453750968</v>
+        <v>0.003653487889096141</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001386928634019569</v>
+        <v>0.002642504405230284</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0006381653365679085</v>
+        <v>0.0326656699180603</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001203326159156859</v>
+        <v>0.0220869779586792</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002575399121269584</v>
+        <v>0.1171137019991875</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.004841941874474287</v>
+        <v>0.1287917196750641</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0008149544009938836</v>
+        <v>0.08780446648597717</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.002222530543804169</v>
+        <v>0.06495370715856552</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0002528703771531582</v>
+        <v>0.03842765837907791</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.002974265487864614</v>
+        <v>0.007730573415756226</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0013181131798774</v>
+        <v>0.04515807330608368</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.00642292806878686</v>
+        <v>0.04602380096912384</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.001897369977086782</v>
+        <v>0.01245001703500748</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.11186954099685e-05</v>
+        <v>0.009737410582602024</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.001232697628438473</v>
+        <v>0.02935288287699223</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.005075058899819851</v>
+        <v>0.09906275570392609</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.001093241618946195</v>
+        <v>0.06380341202020645</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00473662419244647</v>
+        <v>0.02324708737432957</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.007807945366948843</v>
+        <v>0.01223635673522949</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.174424197524786e-05</v>
+        <v>0.04478059709072113</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001030725194141269</v>
+        <v>0.006631441414356232</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002016911283135414</v>
+        <v>0.005507331341505051</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.00232295598834753</v>
+        <v>0.01054369937628508</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001672864891588688</v>
+        <v>0.005282893776893616</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.002918723970651627</v>
+        <v>0.02224022150039673</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001131757046096027</v>
+        <v>0.03657833859324455</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0014966472517699</v>
+        <v>0.01421777624636889</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0005891589098609984</v>
+        <v>0.008804731070995331</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001366160344332457</v>
+        <v>0.00955690536648035</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0008555985987186432</v>
+        <v>0.002302289940416813</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001458868500776589</v>
+        <v>0.03599653393030167</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001380292582325637</v>
+        <v>0.05091944709420204</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002487976802513003</v>
+        <v>0.07514036446809769</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001106512499973178</v>
+        <v>0.03662031888961792</v>
       </c>
       <c r="BZ5" t="n">
-        <v>6.945118366274983e-05</v>
+        <v>0.0223662480711937</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.001449900562874973</v>
+        <v>0.03002592176198959</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.004895597696304321</v>
+        <v>0.03178161382675171</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001950703328475356</v>
+        <v>0.03034490346908569</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001066827331669629</v>
+        <v>0.008903020992875099</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001189031871035695</v>
+        <v>0.0151387806981802</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00116920203436166</v>
+        <v>0.02752006240189075</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.001465643523260951</v>
+        <v>0.03653845191001892</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0008930566255003214</v>
+        <v>0.0005271341651678085</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0007485641399398446</v>
+        <v>0.006286920513957739</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0008282642811536789</v>
+        <v>0.01071701850742102</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001147486153058708</v>
+        <v>0.002848353236913681</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001187486108392477</v>
+        <v>0.020272146910429</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.002800400368869305</v>
+        <v>0.02089260891079903</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0006867056945338845</v>
+        <v>0.03379696607589722</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0003663418756332248</v>
+        <v>0.00416702451184392</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.000684924831148237</v>
+        <v>0.02506206184625626</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00140202627517283</v>
+        <v>0.1703667342662811</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0004514541651587933</v>
+        <v>0.005346486810594797</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0006749760359525681</v>
+        <v>0.03376978263258934</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001228007371537387</v>
+        <v>0.006290878169238567</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001436238875612617</v>
+        <v>0.06251981854438782</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001082194037735462</v>
+        <v>0.01433680206537247</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0007746279006823897</v>
+        <v>0.0002801925875246525</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0003771058400161564</v>
+        <v>0.02979554049670696</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0009390289196744561</v>
+        <v>0.04155812039971352</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0006231116713024676</v>
+        <v>0.001148892100900412</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0005106569151394069</v>
+        <v>0.01869047433137894</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003799961996264756</v>
+        <v>0.01046735607087612</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0009476508130319417</v>
+        <v>0.006545275449752808</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001473020063713193</v>
+        <v>0.00642668129876256</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0003584520891308784</v>
+        <v>0.003624551463872194</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.005597325041890144</v>
+        <v>0.03696800023317337</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.001406701630912721</v>
+        <v>0.08838088810443878</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0004125625127926469</v>
+        <v>0.0269181989133358</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0007432489073835313</v>
+        <v>0.07628247141838074</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004900660831481218</v>
+        <v>0.01286140270531178</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.005513282958418131</v>
+        <v>0.0002383803948760033</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0008696946897543967</v>
+        <v>0.1037322878837585</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.001879101851955056</v>
+        <v>0.01654118858277798</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0007840306498110294</v>
+        <v>0.01457294262945652</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0008250988903455436</v>
+        <v>0.01494250912219286</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001963001908734441</v>
+        <v>0.003751928685232997</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0004273812228348106</v>
+        <v>0.02055380120873451</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.002389900153502822</v>
+        <v>0.0357903316617012</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0004966006963513792</v>
+        <v>0.01088866963982582</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001182638923637569</v>
+        <v>0.01875404268503189</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0009038957068696618</v>
+        <v>0.007551667280495167</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0008184693288058043</v>
+        <v>0.07651370763778687</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0002613988472148776</v>
+        <v>0.03165632858872414</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0002562492154538631</v>
+        <v>0.0008371190633624792</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.000988186220638454</v>
+        <v>0.01267766021192074</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0008258828893303871</v>
+        <v>0.03147773444652557</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0005649402737617493</v>
+        <v>0.005770529620349407</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003196768462657928</v>
+        <v>0.05992406979203224</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0003905344929080456</v>
+        <v>0.02509496361017227</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002219465794041753</v>
+        <v>0.02458496764302254</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.001553516834974289</v>
+        <v>0.02300519309937954</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.00113822880666703</v>
+        <v>0.009389951825141907</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0005696538137272</v>
+        <v>0.003562912344932556</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.00110690260771662</v>
+        <v>0.02014660462737083</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001896919100545347</v>
+        <v>0.04058217257261276</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.000823211157694459</v>
+        <v>0.02889788150787354</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0003846350882668048</v>
+        <v>0.005441118031740189</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0007880814955569804</v>
+        <v>0.006825048010796309</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001222143182530999</v>
+        <v>0.01858636364340782</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001942058093845844</v>
+        <v>0.01739164814352989</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001081985654309392</v>
+        <v>0.003105472773313522</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001199075923068449</v>
+        <v>0.03831824660301208</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001530077192001045</v>
+        <v>0.006533503532409668</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0009126507793553174</v>
+        <v>0.05335106700658798</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0005043951096013188</v>
+        <v>0.0001036971807479858</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0007794291013851762</v>
+        <v>0.04681215062737465</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0007320459117181599</v>
+        <v>0.03402235358953476</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.003567018546164036</v>
+        <v>0.01063445396721363</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001294807298108935</v>
+        <v>0.04509389027953148</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0008722556522116065</v>
+        <v>0.009386097081005573</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.000977618619799614</v>
+        <v>0.01498815789818764</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0008326325914822519</v>
+        <v>0.02936319075524807</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001136623905040324</v>
+        <v>0.04027429223060608</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0003865354810841382</v>
+        <v>0.008798933587968349</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0007346062920987606</v>
+        <v>0.0121548343449831</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0005332141881808639</v>
+        <v>0.01228443440049887</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0008011591853573918</v>
+        <v>0.0191669724881649</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001599938259460032</v>
+        <v>0.004808896221220493</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002369542198721319</v>
+        <v>0.01125910505652428</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0007308374624699354</v>
+        <v>0.001339870039373636</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001556800561957061</v>
+        <v>0.05759021639823914</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.002194158034399152</v>
+        <v>0.01702874712646008</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0006378524703904986</v>
+        <v>0.04360082373023033</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001392765319906175</v>
+        <v>0.02586403675377369</v>
       </c>
       <c r="FM5" t="n">
-        <v>5.405758565757424e-05</v>
+        <v>0.0102817490696907</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0006687392015010118</v>
+        <v>0.008994731120765209</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001935911946929991</v>
+        <v>0.04961251467466354</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.002586983144283295</v>
+        <v>0.06572321802377701</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002173617947846651</v>
+        <v>0.005307720974087715</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.004843870177865028</v>
+        <v>0.02184555120766163</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002286647679284215</v>
+        <v>0.02353281155228615</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0006391943315975368</v>
+        <v>0.02690758183598518</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002637795405462384</v>
+        <v>0.04513233155012131</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004219089751131833</v>
+        <v>0.009521957486867905</v>
       </c>
       <c r="FW5" t="n">
-        <v>9.833845251705498e-05</v>
+        <v>0.0663454458117485</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001939541776664555</v>
+        <v>0.03109097480773926</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0009698198409751058</v>
+        <v>0.011744549497962</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001006074715405703</v>
+        <v>0.04081793874502182</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001617045374587178</v>
+        <v>0.03537971898913383</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001691419631242752</v>
+        <v>0.04887007176876068</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.003224252024665475</v>
+        <v>0.07155238091945648</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.003019514959305525</v>
+        <v>0.04502217099070549</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0003931975807063282</v>
+        <v>0.0547364316880703</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001270680804736912</v>
+        <v>0.01031894702464342</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0008185729384422302</v>
+        <v>0.008028717711567879</v>
       </c>
     </row>
     <row r="6">
@@ -3844,5123 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001269344007596374</v>
+        <v>1.498994151916122e-05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03074840269982815</v>
+        <v>3.343162825331092e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002112050773575902</v>
+        <v>4.450579581316561e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01172876171767712</v>
+        <v>5.254462848824915e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0085768923163414</v>
+        <v>1.190628609037958e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01022484712302685</v>
+        <v>2.063142164843157e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.710101246833801e-05</v>
+        <v>1.52319098560838e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004258895292878151</v>
+        <v>2.191798375861254e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001519414596259594</v>
+        <v>1.542706195323262e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004102971870452166</v>
+        <v>1.434892510587815e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02509531378746033</v>
+        <v>4.531714512268081e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001235163421370089</v>
+        <v>4.056625584780704e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008335614576935768</v>
+        <v>1.867194987426046e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007123860996216536</v>
+        <v>1.794408308342099e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01215117797255516</v>
+        <v>2.617184873088263e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001066650962457061</v>
+        <v>9.779237188922707e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003427333198487759</v>
+        <v>4.038111910631415e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0007585652056150138</v>
+        <v>2.792970553855412e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0006767035229131579</v>
+        <v>3.207610006938921e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003741806140169501</v>
+        <v>5.697388587577734e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009920216398313642</v>
+        <v>7.003083055678871e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004721658769994974</v>
+        <v>1.260597491636872e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004108764231204987</v>
+        <v>5.925854566157795e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001779204118065536</v>
+        <v>5.156628503755201e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001129148993641138</v>
+        <v>1.908320882648695e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003246225183829665</v>
+        <v>7.171327524702065e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001309362472966313</v>
+        <v>3.25226528730127e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001533316099084914</v>
+        <v>2.255042545584729e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.004264970775693655</v>
+        <v>1.742001950333361e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0009099742164835334</v>
+        <v>6.444696737162303e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001839240314438939</v>
+        <v>9.699740076030139e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.003286999184638262</v>
+        <v>2.270681943628006e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0017137685790658</v>
+        <v>6.905796908540651e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.001790934009477496</v>
+        <v>1.451835032639792e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0001501442166045308</v>
+        <v>2.684503670025151e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001959991874173284</v>
+        <v>4.775838533532806e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00485652033239603</v>
+        <v>2.756480171228759e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003408907447010279</v>
+        <v>5.102884188090684e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0004074843600392342</v>
+        <v>6.073436907172436e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001486699329689145</v>
+        <v>4.481345513340784e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>7.250491762533784e-06</v>
+        <v>3.386654498171993e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.003076719352975488</v>
+        <v>4.866108156420523e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0009243245585821569</v>
+        <v>4.553611688606907e-06</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.001810787594877183</v>
+        <v>1.174725639430108e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001806389889679849</v>
+        <v>2.112755282723811e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0007002835627645254</v>
+        <v>1.032219006447122e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.02200134471058846</v>
+        <v>4.139934389968403e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0005058083334006369</v>
+        <v>5.464207788463682e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.002399971708655357</v>
+        <v>4.785830242326483e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004547765129245818</v>
+        <v>1.781173159542959e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.005259753204882145</v>
+        <v>2.184255208703689e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002952928654849529</v>
+        <v>4.221063136355951e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001815105555579066</v>
+        <v>8.958929811342387e-07</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.751663310453296e-05</v>
+        <v>1.105065439332975e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.001072547165676951</v>
+        <v>1.960785994015168e-06</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01008311100304127</v>
+        <v>1.729791983962059e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.006340768653899431</v>
+        <v>3.415584615140688e-07</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001676224172115326</v>
+        <v>1.25641054182779e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.008809305727481842</v>
+        <v>6.013482561684214e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0067974585108459</v>
+        <v>2.130492703145137e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.001598453847691417</v>
+        <v>5.062403033662122e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005686189979314804</v>
+        <v>1.963026988960337e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.002982372883707285</v>
+        <v>6.792315161874285e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003999702166765928</v>
+        <v>3.836552423308603e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.007290775887668133</v>
+        <v>1.287219492951408e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003681986359879375</v>
+        <v>2.143669007637072e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0005668694502674043</v>
+        <v>1.058156158251222e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.003530160989612341</v>
+        <v>7.362735232163686e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.002584748202934861</v>
+        <v>6.637201749981614e-06</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0009161396883428097</v>
+        <v>2.132297595380805e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001258188858628273</v>
+        <v>5.691591013601283e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003063416806980968</v>
+        <v>8.377774065593258e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001202907878905535</v>
+        <v>4.072569936397485e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01226529944688082</v>
+        <v>2.737344948400278e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.004692721180617809</v>
+        <v>4.570342298393371e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002517271088436246</v>
+        <v>1.448080911359284e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0008521892596036196</v>
+        <v>8.645866728329565e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0004320503212511539</v>
+        <v>9.332412446383387e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0007076063775457442</v>
+        <v>4.731673016067361e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0002642183098942041</v>
+        <v>1.08740578070865e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0006586556555703282</v>
+        <v>1.111391156882746e-06</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.000301587744615972</v>
+        <v>1.14041165488743e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.004543624818325043</v>
+        <v>1.011350195767591e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00199669087305665</v>
+        <v>7.358368634413637e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0009338463423773646</v>
+        <v>4.077581706951605e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001369858364341781</v>
+        <v>7.846379617149069e-07</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001669439487159252</v>
+        <v>4.91847777084331e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.00216184533201158</v>
+        <v>5.218258138484089e-06</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001803911873139441</v>
+        <v>3.855242084682686e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0008554772939532995</v>
+        <v>1.665266836425872e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.006167799700051546</v>
+        <v>7.31469026504783e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.006260652560740709</v>
+        <v>6.102531187934801e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.001279403921216726</v>
+        <v>1.309840899921255e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.005341983400285244</v>
+        <v>3.716223091032589e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.004334350116550922</v>
+        <v>3.167466502418392e-06</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0009869015775620937</v>
+        <v>3.483714863250498e-06</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.005153702571988106</v>
+        <v>8.710358088137582e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.003664895426481962</v>
+        <v>2.179803686885862e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0006337811937555671</v>
+        <v>2.005649730563164e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.910755574703217e-05</v>
+        <v>1.419594923390832e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.00368462479673326</v>
+        <v>7.889623702794779e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002912133000791073</v>
+        <v>5.261122737465485e-07</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.002284423913806677</v>
+        <v>1.512857579655247e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0005583970341831446</v>
+        <v>8.908410791264032e-07</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002257504034787416</v>
+        <v>6.174825102789328e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001508261659182608</v>
+        <v>1.043877205120225e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.002378663048148155</v>
+        <v>3.71859869119362e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0006511646788567305</v>
+        <v>7.319677592931839e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.002611462958157063</v>
+        <v>1.372162205370842e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.00279553746804595</v>
+        <v>4.313087174523389e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.002709885593503714</v>
+        <v>5.663368938257918e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01257725805044174</v>
+        <v>4.71281964564696e-08</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.003314664587378502</v>
+        <v>1.394931496179197e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0003666323609650135</v>
+        <v>4.713465841632569e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.005122211761772633</v>
+        <v>3.067995294259163e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0001380734465783462</v>
+        <v>6.211103027453646e-07</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.004856177140027285</v>
+        <v>7.799230843374971e-07</v>
       </c>
       <c r="DN7" t="n">
-        <v>4.621557309292257e-05</v>
+        <v>9.247192792827263e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001718893297947943</v>
+        <v>1.367880486213835e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.003255015704780817</v>
+        <v>6.51814480079338e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0002087668981403112</v>
+        <v>1.115495069825556e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001001805067062378</v>
+        <v>3.075382664974313e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.00206318125128746</v>
+        <v>1.696384606475476e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0003833856026176363</v>
+        <v>3.893108441843651e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0005558135453611612</v>
+        <v>6.410708920157049e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001818817807361484</v>
+        <v>9.932862667483278e-06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0003719549276866019</v>
+        <v>4.747075763589237e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.146938641089946e-05</v>
+        <v>9.156953638012055e-06</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.002879104111343622</v>
+        <v>1.441700533177936e-06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.002459426876157522</v>
+        <v>9.987234079744667e-07</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001321846386417747</v>
+        <v>7.806892426742706e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0005758741754107177</v>
+        <v>1.505114232713822e-05</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0007653118809685111</v>
+        <v>5.90509125686367e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001974980579689145</v>
+        <v>1.315672761847964e-06</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.001334793516434729</v>
+        <v>6.877034138597082e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0003349290345795453</v>
+        <v>3.629715592978755e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.003686000127345324</v>
+        <v>5.020309799874667e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.00065224664285779</v>
+        <v>5.793874152004719e-06</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0003494134871289134</v>
+        <v>1.221047568833455e-06</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0009563197963871062</v>
+        <v>5.542615326703526e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0009348226012662053</v>
+        <v>2.74383046416915e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.002088004723191261</v>
+        <v>5.476356363942614e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001620695926249027</v>
+        <v>6.106032287789276e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0002468872116878629</v>
+        <v>1.293893205911445e-06</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001212134724482894</v>
+        <v>1.340563130725059e-06</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0006191828288137913</v>
+        <v>4.308295501687098e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.003342578420415521</v>
+        <v>5.737102128478e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.001439309446141124</v>
+        <v>8.868437362252735e-07</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001729588024318218</v>
+        <v>9.303232218371704e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.002819835674017668</v>
+        <v>1.383029484713916e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0006800796836614609</v>
+        <v>3.129168135274085e-06</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.006695203948765993</v>
+        <v>5.500536417457624e-07</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0005102805444039404</v>
+        <v>3.855001523334067e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0002227732911705971</v>
+        <v>9.880900506686885e-07</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.003216649172827601</v>
+        <v>1.214423173223622e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001796082360669971</v>
+        <v>4.812363840756007e-08</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.001168404123745859</v>
+        <v>1.445548605261138e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0004997780779376626</v>
+        <v>8.832370781419741e-07</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.001957910601049662</v>
+        <v>3.907283826265484e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.002401933539658785</v>
+        <v>4.979483037459431e-06</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0014280139002949</v>
+        <v>1.779124886525096e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.001340483780950308</v>
+        <v>2.308482862645178e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0009280928061343729</v>
+        <v>9.808187542148517e-07</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.00228593498468399</v>
+        <v>9.230942850990687e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.002703169593587518</v>
+        <v>1.127761333918897e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.006289729382842779</v>
+        <v>8.396618795813993e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.002676985925063491</v>
+        <v>2.211123955930816e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001537252217531204</v>
+        <v>1.161338332167361e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001730140997096896</v>
+        <v>4.594338861352298e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001293163048103452</v>
+        <v>7.397811714326963e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0003631899307947606</v>
+        <v>1.203088413603837e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.002468280494213104</v>
+        <v>1.442995653633261e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.00711023760959506</v>
+        <v>1.741728556226008e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0004366001521702856</v>
+        <v>1.198492918774718e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.002341871149837971</v>
+        <v>1.367388176731765e-05</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.004900312516838312</v>
+        <v>3.500406819512136e-06</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002794500440359116</v>
+        <v>4.295368398743449e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.005349892657250166</v>
+        <v>1.341752977168653e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004222401883453131</v>
+        <v>1.087536747945705e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.003381941700354218</v>
+        <v>1.617343514226377e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.003731011645868421</v>
+        <v>2.208167188655352e-06</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0007876749732531607</v>
+        <v>4.351485586084891e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.002452331362292171</v>
+        <v>5.185825557418866e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0004386028740555048</v>
+        <v>2.682381818885915e-07</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0005646385252475739</v>
+        <v>1.375069314235589e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.00429703202098608</v>
+        <v>1.187830366689013e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.009142754599452019</v>
+        <v>1.780993102329376e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0001026617828756571</v>
+        <v>2.294546902703587e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001527392072603106</v>
+        <v>3.531878064677585e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003926393110305071</v>
+        <v>0.0006265765987336636</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05246670544147491</v>
+        <v>0.001857772469520569</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004813520237803459</v>
+        <v>0.0004023746587336063</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03268513083457947</v>
+        <v>0.0005993762752041221</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008339479565620422</v>
+        <v>0.0004998667282052338</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002529479330405593</v>
+        <v>0.0002391537855146453</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00738661689683795</v>
+        <v>0.0004211445047985762</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005038644187152386</v>
+        <v>0.0003500412858556956</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005479611572809517</v>
+        <v>2.941194907180034e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008975702337920666</v>
+        <v>0.000380342680728063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04106847941875458</v>
+        <v>0.001997087616473436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002883004024624825</v>
+        <v>0.0004636735829990357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03064678609371185</v>
+        <v>0.0009618314215913415</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01292371097952127</v>
+        <v>0.0008184653124772012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008423143997788429</v>
+        <v>0.0001276566181331873</v>
       </c>
       <c r="P8" t="n">
-        <v>0.005231684539467096</v>
+        <v>0.0003716839710250497</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005444451700896025</v>
+        <v>0.0001295961264986545</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002997858915477991</v>
+        <v>0.000238122243899852</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002582047134637833</v>
+        <v>0.0001868944091256708</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009267079643905163</v>
+        <v>3.862626908812672e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002495101420208812</v>
+        <v>0.0002329896378796548</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003290383378043771</v>
+        <v>0.0002037640078924596</v>
       </c>
       <c r="W8" t="n">
-        <v>5.819994839839637e-05</v>
+        <v>0.0001843372010625899</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004618318751454353</v>
+        <v>0.0001036727990140207</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.007247860543429852</v>
+        <v>0.0001728186325635761</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.006324708461761475</v>
+        <v>0.0001701476139714941</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005662203300744295</v>
+        <v>0.0004291998920962214</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001710409764200449</v>
+        <v>0.0002655793796293437</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006159364245831966</v>
+        <v>0.0002120912686223164</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0006977674784138799</v>
+        <v>0.0002387702843407169</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0009761819965206087</v>
+        <v>0.0002867355942726135</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001799715682864189</v>
+        <v>0.0003212754963897169</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00381722510792315</v>
+        <v>0.0004638442769646645</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.00464291637763381</v>
+        <v>8.814949978841469e-05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001902345451526344</v>
+        <v>0.0003472054377198219</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002219285583123565</v>
+        <v>0.0001087960336008109</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.004676287993788719</v>
+        <v>0.0002012886398006231</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.008622813038527966</v>
+        <v>0.0002975764800794423</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000965835468377918</v>
+        <v>0.0001173349228338338</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001411213772371411</v>
+        <v>0.0002408182772342116</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.850760787026957e-05</v>
+        <v>6.876633415231481e-05</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.002494154032319784</v>
+        <v>0.0001866832899395376</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.004037635866552591</v>
+        <v>1.602042175363749e-06</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00335523602552712</v>
+        <v>0.0001194220531033352</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002815861254930496</v>
+        <v>2.028191192948725e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.003154184203594923</v>
+        <v>0.0002114497765433043</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03482317924499512</v>
+        <v>0.001007053768262267</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0005532614886760712</v>
+        <v>7.338310388149694e-05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.007300037425011396</v>
+        <v>0.0002969589259009808</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0009067347273230553</v>
+        <v>0.0009160707122646272</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001260115881450474</v>
+        <v>0.0001078709028661251</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003984976559877396</v>
+        <v>8.361822256119922e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002614026190713048</v>
+        <v>0.0002141380391549319</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002913227304816246</v>
+        <v>4.76176937809214e-05</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.00157369626685977</v>
+        <v>0.0002079902333207428</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.007869929075241089</v>
+        <v>8.665426139486954e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.00788462907075882</v>
+        <v>0.0004089536960236728</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.007666140794754028</v>
+        <v>0.0001762995088938624</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01342947967350483</v>
+        <v>0.0001010910127661191</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001486148801632226</v>
+        <v>7.605219434481114e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005868626292794943</v>
+        <v>0.0001098436041502282</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.005112288054078817</v>
+        <v>0.0004639624385163188</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0006023121532052755</v>
+        <v>6.503725307993591e-05</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.004103887360543013</v>
+        <v>2.0857565687038e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001842000754550099</v>
+        <v>9.712101018521935e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.003075246931985021</v>
+        <v>0.0001006338279694319</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001732515869662166</v>
+        <v>8.206430356949568e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001769472844898701</v>
+        <v>0.0002870954049285501</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.002791839884594083</v>
+        <v>4.51750893262215e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0009074756526388228</v>
+        <v>7.519324572058395e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002383939223363996</v>
+        <v>0.0001104911061702296</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002978365169838071</v>
+        <v>7.098095375113189e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.00384159293025732</v>
+        <v>0.000170816871104762</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02036649920046329</v>
+        <v>0.0007787710055708885</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006425925530493259</v>
+        <v>2.822355600073934e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.007767762057483196</v>
+        <v>0.0001877831236924976</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.469469811534509e-05</v>
+        <v>0.0003280302626080811</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0007752306992188096</v>
+        <v>0.0002497443929314613</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.00390633987262845</v>
+        <v>0.0002928321482613683</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002527345204725862</v>
+        <v>0.0001175848810817115</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.005245299078524113</v>
+        <v>0.0003361191775184125</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001188810681924224</v>
+        <v>5.017617513658479e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.00830356776714325</v>
+        <v>0.0005428754957392812</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003587341867387295</v>
+        <v>0.0001728673814795911</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003260036697611213</v>
+        <v>0.0002190220402553678</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001691676210612059</v>
+        <v>7.323563477257267e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002313041128218174</v>
+        <v>0.0001129046650021337</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001828324398957193</v>
+        <v>7.432496204273775e-06</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0009112139232456684</v>
+        <v>5.653592779708561e-06</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002818240784108639</v>
+        <v>5.279187098494731e-05</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.009417124092578888</v>
+        <v>9.464669710723683e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.00176239712163806</v>
+        <v>0.0003280862292740494</v>
       </c>
       <c r="CO8" t="n">
-        <v>6.247965211514384e-05</v>
+        <v>0.0004106612759642303</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.006459200289100409</v>
+        <v>0.0006015102262608707</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.007802566513419151</v>
+        <v>0.0002108912740368396</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001071776612661779</v>
+        <v>0.0003048546204809099</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.005646455567330122</v>
+        <v>9.528614464215934e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.007427174132317305</v>
+        <v>6.241496157599613e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001265720231458545</v>
+        <v>0.0001166231886600144</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0006968359230086207</v>
+        <v>4.343219188740477e-06</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.007923643104732037</v>
+        <v>0.0005294422153383493</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003992064855992794</v>
+        <v>0.0001604148710612208</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.005018406081944704</v>
+        <v>0.0002709440886974335</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002569132717326283</v>
+        <v>0.0001562225806992501</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.003328451421111822</v>
+        <v>0.0001108871001633815</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001809339853934944</v>
+        <v>2.952821887447499e-06</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001735667348839343</v>
+        <v>2.288566429342609e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001062206691130996</v>
+        <v>0.0001253054797416553</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.003622776130214334</v>
+        <v>0.0002927847963292152</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.007265308871865273</v>
+        <v>0.0005665713688358665</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0002262101043015718</v>
+        <v>9.552088158670813e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01414309628307819</v>
+        <v>0.0002764930832199752</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001880557858385146</v>
+        <v>0.0002755160385277122</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002873031888157129</v>
+        <v>0.0005781367653980851</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.00415338296443224</v>
+        <v>8.002755930647254e-05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001568197039887309</v>
+        <v>0.0002693042624741793</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.000964085222221911</v>
+        <v>0.0003001404402311891</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0009602044592611492</v>
+        <v>5.951678758719936e-07</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001574531081132591</v>
+        <v>0.0003479463048279285</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.00239873118698597</v>
+        <v>0.0001835981820477173</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0009970343671739101</v>
+        <v>0.0001831279369071126</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.004970334004610777</v>
+        <v>9.399680493515916e-06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.003957878332585096</v>
+        <v>7.61900664656423e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.002469303552061319</v>
+        <v>0.0001724745961837471</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.004207929130643606</v>
+        <v>0.0001291485677938908</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.005453589372336864</v>
+        <v>0.0003837217809632421</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0008479771786369383</v>
+        <v>0.0001445593370590359</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003361482406035066</v>
+        <v>0.000208517027203925</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0043103345669806</v>
+        <v>8.289897959912196e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.003003180958330631</v>
+        <v>3.14462959067896e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.004060502164065838</v>
+        <v>0.0001395723666064441</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004323380999267101</v>
+        <v>0.0003639823698904365</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002968995366245508</v>
+        <v>6.866625335533172e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001668279990553856</v>
+        <v>0.0005477452650666237</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.002957620657980442</v>
+        <v>0.0004458465555217117</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.001559213735163212</v>
+        <v>4.398442979436368e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.005520162172615528</v>
+        <v>0.0004462642536964267</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.003255293471738696</v>
+        <v>6.409347406588495e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.003767688293009996</v>
+        <v>0.0002433089102851227</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0008602687157690525</v>
+        <v>7.364447810687125e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.004517406690865755</v>
+        <v>3.045145786018111e-05</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001510289264842868</v>
+        <v>9.845016029430553e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0004110515583306551</v>
+        <v>3.884477337123826e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001346522592939436</v>
+        <v>0.0001156964208348654</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0003646995173767209</v>
+        <v>5.37325358891394e-05</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.004803246818482876</v>
+        <v>0.0003508718800731003</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.005674523767083883</v>
+        <v>1.652121136430651e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002831059275195003</v>
+        <v>0.0002149362699128687</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003415822284296155</v>
+        <v>0.000117517338367179</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.00789556372910738</v>
+        <v>0.0002491092309355736</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.004318176303058863</v>
+        <v>0.0001718689600238577</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.006111091002821922</v>
+        <v>2.809534407788306e-06</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0007349764346145093</v>
+        <v>0.0001797040895326063</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0005017595831304789</v>
+        <v>4.210577390040271e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.008237557485699654</v>
+        <v>0.0006179432384669781</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.002811517100781202</v>
+        <v>0.0001480835489928722</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00492078484967351</v>
+        <v>0.0002964447485283017</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002367729786783457</v>
+        <v>7.133228064049035e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002889140974730253</v>
+        <v>0.0001566816354170442</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.002537266118451953</v>
+        <v>2.058986865449697e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0009332747431471944</v>
+        <v>1.402962152496912e-05</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.002534299856051803</v>
+        <v>0.0001379973982693627</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001164100831374526</v>
+        <v>1.940662514243741e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.005113052204251289</v>
+        <v>0.0001549567386973649</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.004389046691358089</v>
+        <v>0.0001729430514387786</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.005687073804438114</v>
+        <v>0.0001600934920134023</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.001723758410662413</v>
+        <v>2.941989805549383e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.002070015296339989</v>
+        <v>0.0002134974638465792</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0007224373985081911</v>
+        <v>7.421301415888593e-05</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0005839747027494013</v>
+        <v>0.0001544897968415171</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001853431924246252</v>
+        <v>4.962967068422586e-05</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001325095538049936</v>
+        <v>0.0002343658852623776</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.008869342505931854</v>
+        <v>5.187447823118418e-05</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.006910108961164951</v>
+        <v>1.563108526170254e-05</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005862513557076454</v>
+        <v>0.0001656990789342672</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0003298365918453783</v>
+        <v>3.144774382235482e-05</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001450314885005355</v>
+        <v>0.0002341923245694488</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.001217849436216056</v>
+        <v>0.0001413354038959369</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.002329892944544554</v>
+        <v>0.0001448274997528642</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.002395848510786891</v>
+        <v>0.0004736734554171562</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.007254039403051138</v>
+        <v>0.0002586836635600775</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0001330204104306176</v>
+        <v>0.000360768404789269</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0002980357094202191</v>
+        <v>0.0001886981190182269</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0003908228245563805</v>
+        <v>0.000212779501453042</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.006618043407797813</v>
+        <v>0.0002704570943024009</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.004734725691378117</v>
+        <v>0.0001734186662361026</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01910966821014881</v>
+        <v>0.0002391847665421665</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.002885036868974566</v>
+        <v>5.619294825010002e-06</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.004414864350110292</v>
+        <v>0.0001655965315876529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0007945320103317499</v>
+        <v>0.0006431235233321786</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03279321268200874</v>
+        <v>0.001068972400389612</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000137317183543928</v>
+        <v>8.330494165420532e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01365689467638731</v>
+        <v>0.0002632157411426306</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007852254435420036</v>
+        <v>2.868309093173593e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01916059665381908</v>
+        <v>2.442274853819981e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002842643298208714</v>
+        <v>0.0002899225219152868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0100134564563632</v>
+        <v>0.0002372647140873596</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001666995813138783</v>
+        <v>0.0001300477888435125</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005691471043974161</v>
+        <v>0.0005671374965459108</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02714700624346733</v>
+        <v>0.00129779998678714</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00312227732501924</v>
+        <v>0.0002869208692573011</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009916592389345169</v>
+        <v>0.000898670987226069</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006101277656853199</v>
+        <v>0.0001765518100000918</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02191941440105438</v>
+        <v>0.0001847572129918262</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001089888974092901</v>
+        <v>2.873196717700921e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001879858784377575</v>
+        <v>0.0002084883599309251</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001484089298173785</v>
+        <v>0.0003897011047229171</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002816064050421119</v>
+        <v>0.0001031974461511709</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004611257463693619</v>
+        <v>0.0002504676522221416</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002060357946902514</v>
+        <v>3.705155540956184e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003169072791934013</v>
+        <v>2.929859329015017e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003302703145891428</v>
+        <v>5.27369265910238e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0007768380455672741</v>
+        <v>0.0001184832653962076</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003340849885717034</v>
+        <v>0.0001194003198179416</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002848071046173573</v>
+        <v>0.0002022893604589626</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003656190820038319</v>
+        <v>9.502342436462641e-05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009584126528352499</v>
+        <v>6.496713467640802e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.004334692843258381</v>
+        <v>4.457233808352612e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.001013431348837912</v>
+        <v>6.348629540298134e-06</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.000520087662152946</v>
+        <v>0.0002412083558738232</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0009482646710239351</v>
+        <v>0.0003847916959784925</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001552089466713369</v>
+        <v>0.000208540222956799</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002144700614735484</v>
+        <v>2.198717265855521e-05</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001955399755388498</v>
+        <v>0.000532144564203918</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00146585307084024</v>
+        <v>7.802726759109646e-05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004620651248842478</v>
+        <v>1.192609306599479e-05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.005354519002139568</v>
+        <v>1.272047302336432e-05</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.000822673027869314</v>
+        <v>9.118557500187308e-05</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001500844955444336</v>
+        <v>2.483360731275752e-05</v>
       </c>
       <c r="AO9" t="n">
-        <v>3.465195186436176e-05</v>
+        <v>0.0001464892993681133</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.005250699818134308</v>
+        <v>0.0001652281498536468</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.800607424229383e-05</v>
+        <v>0.0001143729969044216</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003201475366950035</v>
+        <v>0.0004140421224292368</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003553390270099044</v>
+        <v>0.0001757332793204114</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001592225511558354</v>
+        <v>0.0002736333990469575</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.02270201593637466</v>
+        <v>0.0008998975390568376</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0008586632320657372</v>
+        <v>4.151345274294727e-05</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001777677214704454</v>
+        <v>4.739472569781356e-05</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.004793669562786818</v>
+        <v>0.0006289953016676009</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01269099675118923</v>
+        <v>0.0004403777129482478</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.000195751286810264</v>
+        <v>5.138038977747783e-05</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004854196682572365</v>
+        <v>0.0001212693678098731</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00529345590621233</v>
+        <v>8.245447679655626e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0008048766758292913</v>
+        <v>0.0002318477781955153</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00737994397059083</v>
+        <v>0.0001416304148733616</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.009075912646949291</v>
+        <v>7.523546082666144e-05</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.003002265235409141</v>
+        <v>0.0001231096975971013</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.006181759759783745</v>
+        <v>2.407239662716165e-05</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004617527592927217</v>
+        <v>6.769302854081616e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002386845182627439</v>
+        <v>0.0002097440737998113</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00559712341055274</v>
+        <v>0.0002046490699285641</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.891445860266685e-05</v>
+        <v>0.0001399748289259151</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001021137810312212</v>
+        <v>4.084355168743059e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.006156382616609335</v>
+        <v>0.0002907312591560185</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.003340107388794422</v>
+        <v>3.2855477911653e-05</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001239888137206435</v>
+        <v>0.0002734331937972456</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002295345300808549</v>
+        <v>0.0002745878591667861</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.002668557222932577</v>
+        <v>3.744426430785097e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001966075506061316</v>
+        <v>0.000187002937309444</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001346496283076704</v>
+        <v>0.0001518720528110862</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001980796456336975</v>
+        <v>8.855017949827015e-05</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.002208706922829151</v>
+        <v>2.795605178107508e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01236043684184551</v>
+        <v>0.0007637676317244768</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0034915073774755</v>
+        <v>8.853584586177021e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.003704386996105313</v>
+        <v>0.0002241166221210733</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.004220868460834026</v>
+        <v>6.718194345012307e-05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.003416845109313726</v>
+        <v>8.276492008008063e-05</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002302889944985509</v>
+        <v>0.0002013459452427924</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001690911129117012</v>
+        <v>2.268145181005821e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004370769951492548</v>
+        <v>0.0001478430785937235</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0004313722893130034</v>
+        <v>0.0001602514821570367</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.005193030461668968</v>
+        <v>0.0002816843043547124</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.003433668054640293</v>
+        <v>8.012661965040024e-06</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002236786298453808</v>
+        <v>0.0001166825531981885</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001412317040376365</v>
+        <v>5.210591552895494e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002998632844537497</v>
+        <v>3.05598478007596e-05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001627574441954494</v>
+        <v>2.404342376394197e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001644565491005778</v>
+        <v>7.10364111000672e-06</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002169742016121745</v>
+        <v>3.442999513936229e-06</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.005347506608814001</v>
+        <v>0.0001125701382989064</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003229243448004127</v>
+        <v>0.0006173382280394435</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.002203280804678798</v>
+        <v>0.0002841907553374767</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002141829580068588</v>
+        <v>7.972712774062529e-05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001811605296097696</v>
+        <v>0.0002484052674844861</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.00231798505410552</v>
+        <v>0.0001027967082336545</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.005805563181638718</v>
+        <v>5.311391578288749e-05</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.005676781758666039</v>
+        <v>1.910437276819721e-05</v>
       </c>
       <c r="CU9" t="n">
-        <v>7.825711509212852e-05</v>
+        <v>5.022832192480564e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.250465331599116e-05</v>
+        <v>8.94942568265833e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.004044972825795412</v>
+        <v>0.0002964706800412387</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.003951192833483219</v>
+        <v>1.164886998594739e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.004032949917018414</v>
+        <v>0.0001166515357908793</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0008747185347601771</v>
+        <v>4.896830068901181e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.003308021696284413</v>
+        <v>3.251543603255413e-05</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.00158735690638423</v>
+        <v>7.479674241039902e-05</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.003595886984840035</v>
+        <v>3.292039036750793e-05</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001065308460965753</v>
+        <v>5.756278187618591e-05</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003554507158696651</v>
+        <v>0.0005044267745688558</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.00434246938675642</v>
+        <v>2.628155561978929e-05</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0002668522647581995</v>
+        <v>0.0001227896282216534</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01385816466063261</v>
+        <v>0.0002360704820603132</v>
       </c>
       <c r="DI9" t="n">
-        <v>9.661224612500519e-05</v>
+        <v>0.000233345796004869</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0007406303193420172</v>
+        <v>0.0003348206519149244</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.004721783101558685</v>
+        <v>4.36595146311447e-05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.003793752985075116</v>
+        <v>2.184375262004323e-05</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001177491620182991</v>
+        <v>4.325816189520992e-05</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001478597638197243</v>
+        <v>9.03138643479906e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0007030065171420574</v>
+        <v>0.0001549574226373807</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.002187997102737427</v>
+        <v>0.0001033078006003052</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001555769238620996</v>
+        <v>0.0004080938233528286</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003986497758887708</v>
+        <v>5.251520269666798e-05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001028470462188125</v>
+        <v>0.0002369093563174829</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003745338181033731</v>
+        <v>3.117178857792169e-05</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001100803609006107</v>
+        <v>0.0002559772983659059</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.003525620559230447</v>
+        <v>0.0001152960467152297</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.00128403992857784</v>
+        <v>0.00010468672553543</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.002855394966900349</v>
+        <v>0.0002564757887739688</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.006801391951739788</v>
+        <v>0.000323099666275084</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.000464346376247704</v>
+        <v>0.0001621127157704905</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001464747241698205</v>
+        <v>0.0003321614640299231</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0009468329371884465</v>
+        <v>5.361839157558279e-06</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0005552166840061545</v>
+        <v>3.472145181149244e-05</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001502695144154131</v>
+        <v>0.0004277954285498708</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001258184784092009</v>
+        <v>0.0003173102159053087</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.002048887778073549</v>
+        <v>0.0002602952881716192</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.003526786109432578</v>
+        <v>7.781446765875444e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001375804888084531</v>
+        <v>6.521676550619304e-05</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0004614469944499433</v>
+        <v>0.0004331733798608184</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001250880304723978</v>
+        <v>0.000186205463251099</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.003224961226806045</v>
+        <v>7.736714178463444e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001458112616091967</v>
+        <v>3.118797758361325e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0006347126327455044</v>
+        <v>0.0001435950689483434</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0006833340157754719</v>
+        <v>3.148028190480545e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0004406757070682943</v>
+        <v>2.987532207043841e-05</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001290935906581581</v>
+        <v>6.589206168428063e-05</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.005888385698199272</v>
+        <v>4.83401890960522e-06</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.003316933754831553</v>
+        <v>3.080160240642726e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.002007017843425274</v>
+        <v>0.0005082425777800381</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003959718160331249</v>
+        <v>0.0002510283375158906</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.004264509305357933</v>
+        <v>0.000156484340550378</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0076321205124259</v>
+        <v>0.0001055353786796331</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003301044926047325</v>
+        <v>0.0001577821094542742</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002716311428230256</v>
+        <v>0.0001058075358741917</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.004105135332792997</v>
+        <v>0.0003727947769220918</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.002931306604295969</v>
+        <v>1.803730083338451e-05</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.002485230565071106</v>
+        <v>0.0001441612403141335</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.00137367204297334</v>
+        <v>3.690451558213681e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.00308255129493773</v>
+        <v>3.771141928154975e-05</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.002754860790446401</v>
+        <v>1.542040990898386e-05</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.002281344961374998</v>
+        <v>5.493516800925136e-05</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.002233779523521662</v>
+        <v>5.449731179396622e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0004646669840440154</v>
+        <v>6.547936936840415e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.002403598045930266</v>
+        <v>0.0002310520794708282</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.00564786558970809</v>
+        <v>0.0001195077347801998</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.003315052017569542</v>
+        <v>0.0004153238551225513</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0008573322556912899</v>
+        <v>0.0001623456337256357</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.002277221530675888</v>
+        <v>8.669164526509121e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0003853672824334353</v>
+        <v>0.000113886155304499</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.002005946123972535</v>
+        <v>6.11337018199265e-05</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.001690006116405129</v>
+        <v>0.000226941003347747</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001346351578831673</v>
+        <v>0.0004884956870228052</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.007230111863464117</v>
+        <v>0.0003076943394262344</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.003796092001721263</v>
+        <v>0.0002461551339365542</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.00237959180958569</v>
+        <v>0.0001907174591906369</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.001019389368593693</v>
+        <v>0.0005760933854617178</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002503657480701804</v>
+        <v>9.774935460882261e-05</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.002765449229627848</v>
+        <v>0.0002319326595170423</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.002076355507597327</v>
+        <v>0.000225334835704416</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0005379795911721885</v>
+        <v>0.0001430625125067309</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.005587590858340263</v>
+        <v>0.000114438465971034</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002123802667483687</v>
+        <v>1.968299693544395e-05</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.002465478843078017</v>
+        <v>0.00017495259817224</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.001312705688178539</v>
+        <v>0.0003701186215039343</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.003288572421297431</v>
+        <v>9.612692520022392e-05</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.004680703859776258</v>
+        <v>0.0001213793875649571</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.01504726614803076</v>
+        <v>3.621445284807123e-05</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0005728439427912235</v>
+        <v>9.667496487963945e-05</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.002433954970911145</v>
+        <v>0.0002025929716182873</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.002166565507650375</v>
+        <v>5.643873350891226e-07</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01046797819435596</v>
+        <v>3.320625410196953e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001234503462910652</v>
+        <v>5.30961585809564e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006206530146300793</v>
+        <v>2.221840077254456e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002090177964419127</v>
+        <v>9.580304549672292e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002654185285791755</v>
+        <v>2.753533294708177e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001190116629004478</v>
+        <v>8.619491609351826e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002563571033533663</v>
+        <v>9.184807936435391e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0004424895159900188</v>
+        <v>4.121911700849523e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002873767632991076</v>
+        <v>1.747889797343305e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007251882459968328</v>
+        <v>3.585351350920973e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006494410918094218</v>
+        <v>7.018329597485717e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>0.004613902885466814</v>
+        <v>3.604860467021354e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.002814234234392643</v>
+        <v>1.61058119374502e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003914650529623032</v>
+        <v>4.945007958667702e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001553986803628504</v>
+        <v>6.558129825862125e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001574035733938217</v>
+        <v>2.630717403917515e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>2.256622246932238e-05</v>
+        <v>2.023648164595215e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>8.355315367225558e-05</v>
+        <v>3.196206250777323e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00163679919205606</v>
+        <v>2.675668042684265e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000387699663406238</v>
+        <v>2.183863330174063e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001054267748259008</v>
+        <v>4.182737143310078e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0006993223214522004</v>
+        <v>3.436051940752805e-07</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001321951975114644</v>
+        <v>3.455972716892575e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001824429607950151</v>
+        <v>1.187215943332376e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0003517487493809313</v>
+        <v>3.629608613664459e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001106176874600351</v>
+        <v>6.073124723116052e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0002765379031188786</v>
+        <v>3.580716168016806e-08</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.001002489705570042</v>
+        <v>1.993838196767683e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001209838665090501</v>
+        <v>3.187114998581819e-07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001218482066178694</v>
+        <v>3.631938056969375e-07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0002925292938016355</v>
+        <v>6.742196774212061e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.992955367313698e-05</v>
+        <v>6.50528306778142e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001076241722330451</v>
+        <v>4.740142856007878e-08</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0005228507798165083</v>
+        <v>8.864613505465968e-07</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002239656314486638</v>
+        <v>5.355396837103399e-08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001141775632277131</v>
+        <v>2.478400347172283e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001387676107697189</v>
+        <v>3.183874639489659e-07</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0003900541050825268</v>
+        <v>1.551702268898225e-07</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0002992695372086018</v>
+        <v>2.599659580937441e-07</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0003007582272402942</v>
+        <v>7.316962324921406e-08</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0005359268980100751</v>
+        <v>5.182336053621839e-07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0007700460264459252</v>
+        <v>2.672582013474312e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.752534005092457e-05</v>
+        <v>1.204470265747659e-07</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0008820208022370934</v>
+        <v>6.069517155538051e-08</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.000179827053216286</v>
+        <v>3.563557129382389e-07</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.006812069565057755</v>
+        <v>2.047574753305526e-06</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0001501702063251287</v>
+        <v>4.265936937031256e-08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001452934113331139</v>
+        <v>8.221884399972623e-07</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.649009785382077e-05</v>
+        <v>1.724332946650975e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0007314424146898091</v>
+        <v>3.187003017046663e-07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.286617200297769e-05</v>
+        <v>5.242416634132496e-08</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0008726973901502788</v>
+        <v>2.759638846328016e-07</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001115904771722853</v>
+        <v>5.202049635499861e-08</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.001131570083089173</v>
+        <v>5.544231385101739e-08</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0019469402031973</v>
+        <v>8.235879533913248e-08</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.002000664826482534</v>
+        <v>6.07193726409605e-07</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001281998469494283</v>
+        <v>5.168257075638394e-07</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.003052669577300549</v>
+        <v>4.663737342980312e-07</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001236964832060039</v>
+        <v>1.8280611868704e-07</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0008402736857533455</v>
+        <v>1.641031417420891e-07</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.002004459267482162</v>
+        <v>9.193860250888974e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0003342347918078303</v>
+        <v>1.272584881917282e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001362391747534275</v>
+        <v>8.211685553760617e-08</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001199962920509279</v>
+        <v>3.635146015312785e-07</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0008085068548098207</v>
+        <v>5.912959721854349e-08</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0005492966156452894</v>
+        <v>5.446335080705467e-07</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0008272686973214149</v>
+        <v>3.091271025823517e-07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0004128797445446253</v>
+        <v>1.759045886728927e-07</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0005414913757704198</v>
+        <v>3.950756877202366e-07</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.000992948655039072</v>
+        <v>2.740481193086453e-07</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0001851577253546566</v>
+        <v>3.80050977355495e-08</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0001090302394004539</v>
+        <v>2.926820741322445e-07</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.003450854914262891</v>
+        <v>1.559888232804951e-06</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001425254158675671</v>
+        <v>5.931154589688958e-08</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0008779330528341234</v>
+        <v>8.845906904753065e-07</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001765844790497795</v>
+        <v>4.61695208286983e-07</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0008690162794664502</v>
+        <v>3.987990453424572e-07</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.001408298034220934</v>
+        <v>3.776332562210882e-07</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0002131459332304075</v>
+        <v>1.052244300581151e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0007132255705073476</v>
+        <v>4.318762307775614e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0004123435355722904</v>
+        <v>2.76282463573807e-08</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001654567080549896</v>
+        <v>8.946553862188011e-07</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0008412490715272725</v>
+        <v>2.322608594340636e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0004327366477809846</v>
+        <v>6.692706051580899e-07</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0005043764249421656</v>
+        <v>1.162552791811322e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0008282770868390799</v>
+        <v>1.098983126723851e-08</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0003860199358314276</v>
+        <v>1.533349092142089e-08</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0002423798723611981</v>
+        <v>1.104069582424927e-07</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0006960618775337934</v>
+        <v>6.588938816776135e-08</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0009753967169672251</v>
+        <v>3.647756443569961e-07</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0001802195911295712</v>
+        <v>9.236454161509755e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>2.853402111213654e-05</v>
+        <v>7.530717311965418e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.001990515273064375</v>
+        <v>1.069243921847374e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001550364075228572</v>
+        <v>1.334802561814286e-07</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.000137570226797834</v>
+        <v>5.061364163339022e-07</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.001202845247462392</v>
+        <v>2.40550548369356e-07</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001069715828634799</v>
+        <v>2.892581392188731e-07</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0002151808876078576</v>
+        <v>2.163320544923408e-07</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0003185647074133158</v>
+        <v>8.32898763292178e-08</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001395351020619273</v>
+        <v>9.783957466424908e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0007277673576027155</v>
+        <v>2.350132888295775e-07</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0009469192591495812</v>
+        <v>7.791645089127996e-07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0006072693504393101</v>
+        <v>1.605167909701777e-07</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.000962578400503844</v>
+        <v>4.532866526574253e-08</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0004281966830603778</v>
+        <v>3.472299781037691e-09</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0002812421007547528</v>
+        <v>8.873608692283597e-08</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0004205705772619694</v>
+        <v>1.542034482326926e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.000840037246234715</v>
+        <v>8.794071391093894e-07</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0008445130079053342</v>
+        <v>6.725406365148956e-07</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001472093397751451</v>
+        <v>9.175757043067279e-08</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.004991857334971428</v>
+        <v>1.012709503811493e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.002161675598472357</v>
+        <v>3.034132589618821e-07</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0009018041891977191</v>
+        <v>9.411644441570388e-07</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0004837192827835679</v>
+        <v>4.501172412574306e-08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001363074406981468</v>
+        <v>9.696663028080366e-07</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0003432419034652412</v>
+        <v>3.584781040899543e-07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.000612858566455543</v>
+        <v>1.540624765539178e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.000589484057854861</v>
+        <v>4.486962552618934e-07</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0007916422327980399</v>
+        <v>2.524037086004682e-07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.000165687597473152</v>
+        <v>1.58950726358853e-07</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0012954983394593</v>
+        <v>1.629847901085668e-07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0008766978280618787</v>
+        <v>1.653658614486631e-07</v>
       </c>
       <c r="DT10" t="n">
-        <v>3.183133685524808e-07</v>
+        <v>2.604614053325349e-07</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0001185957080451772</v>
+        <v>7.241272896862938e-07</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001297847600653768</v>
+        <v>7.850560450606281e-07</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0004883857909590006</v>
+        <v>1.006049501484085e-07</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.000356926757376641</v>
+        <v>6.276976591834682e-07</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001802361686713994</v>
+        <v>1.228338533110218e-07</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0001058964335243218</v>
+        <v>4.214096520627209e-07</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001396189909428358</v>
+        <v>1.040099846250087e-07</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00111044233199209</v>
+        <v>4.74359524105239e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0004318988940212876</v>
+        <v>1.994584408748779e-07</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0001577328366693109</v>
+        <v>1.309098252022523e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>2.941202546935529e-05</v>
+        <v>7.689357630624727e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0001710765354800969</v>
+        <v>1.274134291406881e-07</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001010282547213137</v>
+        <v>5.083849714537791e-07</v>
       </c>
       <c r="EH10" t="n">
-        <v>5.289112596074119e-05</v>
+        <v>1.113516745476772e-07</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0004231921921018511</v>
+        <v>7.500460128539999e-07</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0006978517048992217</v>
+        <v>1.018852344714105e-07</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0007906457176432014</v>
+        <v>6.17379356526726e-08</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0009810738265514374</v>
+        <v>6.313567979532309e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0002451882464811206</v>
+        <v>2.717779779004559e-08</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0002727995743043721</v>
+        <v>1.718115925086749e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0003125258954241872</v>
+        <v>7.032910787074798e-08</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0005763695808127522</v>
+        <v>5.54305472633132e-07</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0007868068059906363</v>
+        <v>4.923607122009344e-08</v>
       </c>
       <c r="ER10" t="n">
-        <v>2.251038677059114e-05</v>
+        <v>6.09567223364138e-07</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0009317885269410908</v>
+        <v>2.848036899649742e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001531703630462289</v>
+        <v>2.265134924073209e-08</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0004733549139928073</v>
+        <v>2.341323863674916e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001815655501559377</v>
+        <v>2.148731539364235e-07</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0006733241607435048</v>
+        <v>4.361834839983203e-07</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002113434311468154</v>
+        <v>5.644886513778147e-08</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.001365896314382553</v>
+        <v>1.081711275219277e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0004566757124848664</v>
+        <v>1.783247682851652e-07</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0006823689327575266</v>
+        <v>8.923577752284473e-07</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0003400935383979231</v>
+        <v>2.04508587842156e-08</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0008793665328994393</v>
+        <v>1.234614472878093e-07</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.00053813261911273</v>
+        <v>9.358809904824739e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001362530892947689</v>
+        <v>1.422460940148085e-07</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.000720395240932703</v>
+        <v>1.758607481860963e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0004272917867638171</v>
+        <v>3.285087402105091e-08</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.000735656707547605</v>
+        <v>2.877927443023509e-07</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001234420924447477</v>
+        <v>3.317382493150944e-07</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001813541748560965</v>
+        <v>6.098304083934636e-07</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0003034829860553145</v>
+        <v>2.833320706940867e-07</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0002967443433590233</v>
+        <v>2.776687608729844e-07</v>
       </c>
       <c r="FM10" t="n">
-        <v>9.526264329906553e-05</v>
+        <v>1.66705177662152e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0009879735298454762</v>
+        <v>1.316358009262331e-07</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0009687514393590391</v>
+        <v>4.80602011521114e-08</v>
       </c>
       <c r="FP10" t="n">
-        <v>2.466549631208181e-06</v>
+        <v>6.576677265002218e-07</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0006031019147485495</v>
+        <v>8.904767128115054e-07</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0007392372936010361</v>
+        <v>2.796993925358038e-08</v>
       </c>
       <c r="FS10" t="n">
-        <v>2.409266016911715e-05</v>
+        <v>4.629651755294617e-07</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.002389470580965281</v>
+        <v>4.734802132588811e-07</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0003923128824681044</v>
+        <v>4.305474874399806e-07</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001090862788259983</v>
+        <v>3.407770634566987e-07</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0005742839421145618</v>
+        <v>3.259221443840943e-07</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0006429253844544291</v>
+        <v>7.222369617920776e-07</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001666984288021922</v>
+        <v>1.080920810636599e-07</v>
       </c>
       <c r="FZ10" t="n">
-        <v>8.868231816450134e-05</v>
+        <v>4.150077188569412e-07</v>
       </c>
       <c r="GA10" t="n">
-        <v>2.711975412239553e-06</v>
+        <v>1.81957801714816e-07</v>
       </c>
       <c r="GB10" t="n">
-        <v>1.569547202961985e-05</v>
+        <v>3.12444058181427e-07</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0008731993730179965</v>
+        <v>5.448367232929741e-07</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.00108347658533603</v>
+        <v>3.237515500131849e-07</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.002954872557893395</v>
+        <v>5.693520392924256e-07</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.00057629169896245</v>
+        <v>2.615128096294939e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.000787570548709482</v>
+        <v>6.09932229167498e-08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03837992623448372</v>
+        <v>0.09360360354185104</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2945789694786072</v>
+        <v>0.2106507271528244</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02956055849790573</v>
+        <v>0.03714218363165855</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2084844708442688</v>
+        <v>0.09773720800876617</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02873272821307182</v>
+        <v>0.117426261305809</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2341400533914566</v>
+        <v>0.05943647772073746</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0123237818479538</v>
+        <v>0.07138680666685104</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1183061897754669</v>
+        <v>0.07349660247564316</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06322909891605377</v>
+        <v>0.05854662135243416</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08260549604892731</v>
+        <v>0.1028127446770668</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2487892508506775</v>
+        <v>0.2715552151203156</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01630603335797787</v>
+        <v>0.06215397641062737</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1763207465410233</v>
+        <v>0.1402927190065384</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0196341872215271</v>
+        <v>0.1198929697275162</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2330509275197983</v>
+        <v>0.02053165808320045</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03541053086519241</v>
+        <v>0.02973649837076664</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01014022156596184</v>
+        <v>0.02411596849560738</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03962930664420128</v>
+        <v>0.1447165161371231</v>
       </c>
       <c r="S11" t="n">
-        <v>0.006562186405062675</v>
+        <v>0.008445017039775848</v>
       </c>
       <c r="T11" t="n">
-        <v>0.005184859968721867</v>
+        <v>0.02015778981149197</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03336030244827271</v>
+        <v>0.01516889780759811</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0539013147354126</v>
+        <v>0.02499627694487572</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07146322727203369</v>
+        <v>0.008106219582259655</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02233741618692875</v>
+        <v>0.006221775431185961</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0257448423653841</v>
+        <v>0.02128000371158123</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05132608115673065</v>
+        <v>0.04323741793632507</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0431319996714592</v>
+        <v>0.01052846200764179</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02818109095096588</v>
+        <v>0.01127174869179726</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.007905134931206703</v>
+        <v>0.007773935794830322</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.03212452679872513</v>
+        <v>0.01805739291012287</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.003669625148177147</v>
+        <v>0.02461361326277256</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02159903571009636</v>
+        <v>0.09502542763948441</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02494514361023903</v>
+        <v>0.03950310871005058</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.002252459526062012</v>
+        <v>0.02739656344056129</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01437826827168465</v>
+        <v>0.06950073689222336</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0241541750729084</v>
+        <v>0.02444403618574142</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04340948164463043</v>
+        <v>0.02758506499230862</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03063660860061646</v>
+        <v>0.0110404035076499</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01838213764131069</v>
+        <v>0.007112959399819374</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.02332080155611038</v>
+        <v>0.0223180390894413</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01611657068133354</v>
+        <v>0.01906326785683632</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.03786054998636246</v>
+        <v>0.06513106822967529</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01391921937465668</v>
+        <v>0.04105016589164734</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.03627727180719376</v>
+        <v>0.112586997449398</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.03520189598202705</v>
+        <v>0.007420018315315247</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.002768121659755707</v>
+        <v>0.09039710462093353</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1732704192399979</v>
+        <v>0.1916689574718475</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.01717520132660866</v>
+        <v>0.008015995845198631</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.07383725792169571</v>
+        <v>0.02867263741791248</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.04371413961052895</v>
+        <v>0.03605011105537415</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1154498383402824</v>
+        <v>0.08085476607084274</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.04714128747582436</v>
+        <v>0.0123643334954977</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.02106650546193123</v>
+        <v>0.01383722200989723</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.07381860911846161</v>
+        <v>0.003015259280800819</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.03033881448209286</v>
+        <v>0.009376266039907932</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07713790982961655</v>
+        <v>0.05003800243139267</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.07756264507770538</v>
+        <v>0.02147427946329117</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.02615742385387421</v>
+        <v>0.08113992214202881</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.02743617817759514</v>
+        <v>0.03581859171390533</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.02615241333842278</v>
+        <v>0.09507232159376144</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.03730317205190659</v>
+        <v>0.07338222861289978</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.02153527177870274</v>
+        <v>0.01687389425933361</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.04019083827733994</v>
+        <v>0.03718584030866623</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01605235412716866</v>
+        <v>0.02679081074893475</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05254020541906357</v>
+        <v>0.02477036230266094</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03780696541070938</v>
+        <v>0.00230636028572917</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01583096385002136</v>
+        <v>0.04035136476159096</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.001976984553039074</v>
+        <v>0.05027422681450844</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.007261347956955433</v>
+        <v>0.02800237387418747</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01816988363862038</v>
+        <v>0.06882812827825546</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02393189072608948</v>
+        <v>0.001625389792025089</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.008733099326491356</v>
+        <v>0.003767244517803192</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.009954320266842842</v>
+        <v>0.05550770461559296</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1038461029529572</v>
+        <v>0.1090773642063141</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.04418233036994934</v>
+        <v>0.01347975805401802</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.06307001411914825</v>
+        <v>0.0454125702381134</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01727957278490067</v>
+        <v>0.01577260717749596</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0812780037522316</v>
+        <v>0.02769427374005318</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.004643460735678673</v>
+        <v>0.0218304805457592</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01908772252500057</v>
+        <v>0.0006498442962765694</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.04683565348386765</v>
+        <v>0.01138137746602297</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.01014438085258007</v>
+        <v>0.00604706909507513</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.04149911180138588</v>
+        <v>0.05407150089740753</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.04232902824878693</v>
+        <v>0.003582656616345048</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02999713830649853</v>
+        <v>0.02563050016760826</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.007893563248217106</v>
+        <v>0.0213905144482851</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03652515634894371</v>
+        <v>0.007259023375809193</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.02032153494656086</v>
+        <v>0.02006785199046135</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.02437444403767586</v>
+        <v>0.0080890953540802</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.03116686455905437</v>
+        <v>0.01121057569980621</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.04193397611379623</v>
+        <v>0.02708770334720612</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01373403426259756</v>
+        <v>0.1119021847844124</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.004307040013372898</v>
+        <v>0.02490247786045074</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.03917759284377098</v>
+        <v>0.04371725395321846</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0006853643571957946</v>
+        <v>0.0006407089531421661</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02546259015798569</v>
+        <v>0.09831635653972626</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.06357265263795853</v>
+        <v>0.02389631979167461</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.03847917914390564</v>
+        <v>0.04505057260394096</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.004840003326535225</v>
+        <v>0.002016136422753334</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.005149221513420343</v>
+        <v>0.005681694950908422</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03916443139314651</v>
+        <v>0.05748511478304863</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.04421691223978996</v>
+        <v>0.00232686591334641</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04195374622941017</v>
+        <v>0.02732973173260689</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.008309546858072281</v>
+        <v>0.03657216578722</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04213190451264381</v>
+        <v>0.002829374745488167</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01859232969582081</v>
+        <v>0.007573269307613373</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.03993063420057297</v>
+        <v>0.01293831132352352</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01934199966490269</v>
+        <v>0.01105464901775122</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.004953333176672459</v>
+        <v>0.04795359447598457</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01022610627114773</v>
+        <v>0.06620706617832184</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01420621015131474</v>
+        <v>0.008942848071455956</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.131739616394043</v>
+        <v>0.03462297841906548</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05312180146574974</v>
+        <v>0.08914395421743393</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01232713554054499</v>
+        <v>0.1231263130903244</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.03362345695495605</v>
+        <v>0.002194516127929091</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.04623018205165863</v>
+        <v>0.006330099888145924</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.04030603542923927</v>
+        <v>0.07187970727682114</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.008042348548769951</v>
+        <v>0.06425103545188904</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.01683894172310829</v>
+        <v>0.02833128347992897</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.02460617385804653</v>
+        <v>0.01752839982509613</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.01211644150316715</v>
+        <v>0.07012862712144852</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.005419318564236164</v>
+        <v>0.009721348062157631</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01477782242000103</v>
+        <v>0.04076600447297096</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.01810738630592823</v>
+        <v>0.001145620364695787</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.002873830962926149</v>
+        <v>0.02365623787045479</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.04039959982037544</v>
+        <v>0.01796765439212322</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.006361281499266624</v>
+        <v>0.03834465891122818</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01455559208989143</v>
+        <v>0.004317020997405052</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.05421287938952446</v>
+        <v>0.02638986706733704</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.01680057123303413</v>
+        <v>0.006196219474077225</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01513343397527933</v>
+        <v>0.00900908000767231</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0433601401746273</v>
+        <v>0.02022788114845753</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0084197036921978</v>
+        <v>0.02568399906158447</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.009416090324521065</v>
+        <v>0.07723738253116608</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01359665114432573</v>
+        <v>0.0891987606883049</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01283395476639271</v>
+        <v>0.01642676815390587</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03980148583650589</v>
+        <v>0.003199303522706032</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.03815652430057526</v>
+        <v>0.004836402833461761</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.007616082206368446</v>
+        <v>0.09635990858078003</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01548765320330858</v>
+        <v>0.05236266180872917</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03097440302371979</v>
+        <v>0.03180214762687683</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.02148771658539772</v>
+        <v>0.01490298565477133</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01449339464306831</v>
+        <v>0.02777071855962276</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0112515352666378</v>
+        <v>0.04458430409431458</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.008891841396689415</v>
+        <v>0.008339935913681984</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01508914399892092</v>
+        <v>0.01552907656878233</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.03127239644527435</v>
+        <v>0.02156596630811691</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0425514318048954</v>
+        <v>0.004138980060815811</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001386278308928013</v>
+        <v>0.07706673443317413</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03571928665041924</v>
+        <v>0.1025614142417908</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0472843237221241</v>
+        <v>0.02606651186943054</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.09077123552560806</v>
+        <v>0.02304739318788052</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0005052355118095875</v>
+        <v>0.001434538513422012</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.003240616293624043</v>
+        <v>0.005033042747527361</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.03078688494861126</v>
+        <v>0.07443279027938843</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0353202149271965</v>
+        <v>0.007166539318859577</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04165896773338318</v>
+        <v>0.03458324074745178</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0119330333545804</v>
+        <v>0.03698620945215225</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03102517127990723</v>
+        <v>0.008731700479984283</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.03848791867494583</v>
+        <v>0.0193895697593689</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.02842466160655022</v>
+        <v>0.0008531030034646392</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.02920215204358101</v>
+        <v>0.01063107419759035</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01987257227301598</v>
+        <v>0.01072322018444538</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.03649252280592918</v>
+        <v>0.09791558235883713</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0364195704460144</v>
+        <v>0.02343231439590454</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.05659700930118561</v>
+        <v>0.0257414672523737</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.002246224554255605</v>
+        <v>0.0355955958366394</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.004853134043514729</v>
+        <v>0.02514151483774185</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.002169007435441017</v>
+        <v>0.006089912727475166</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.02160563878715038</v>
+        <v>0.02068970166146755</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01722986623644829</v>
+        <v>0.09190452098846436</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01824634335935116</v>
+        <v>0.08242732286453247</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0425834134221077</v>
+        <v>0.02038153260946274</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05070240795612335</v>
+        <v>0.03910994157195091</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.06136244162917137</v>
+        <v>0.1654063910245895</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.04526286572217941</v>
+        <v>0.02349994704127312</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04712728038430214</v>
+        <v>0.07456285506486893</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0689186230301857</v>
+        <v>0.1083972230553627</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.009614141657948494</v>
+        <v>0.03592793643474579</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.004281254019588232</v>
+        <v>0.006163539364933968</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.04842210561037064</v>
+        <v>0.02028251625597477</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.02572094462811947</v>
+        <v>0.02039818838238716</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.02831648476421833</v>
+        <v>0.02628624066710472</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.02310745976865292</v>
+        <v>0.02158735692501068</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.003296008333563805</v>
+        <v>0.03226405382156372</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0009515462443232536</v>
+        <v>0.004898573737591505</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1447024494409561</v>
+        <v>0.01719678938388824</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.002518751658499241</v>
+        <v>0.06380834430456161</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.009028416126966476</v>
+        <v>0.04626356065273285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.008299974724650383</v>
+        <v>0.05429346859455109</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3873125314712524</v>
+        <v>0.5525093078613281</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02727349661290646</v>
+        <v>0.1975518018007278</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05286598578095436</v>
+        <v>0.1757754385471344</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1551259607076645</v>
+        <v>0.1587982028722763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01913365162909031</v>
+        <v>0.2772805988788605</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002353314310312271</v>
+        <v>0.1246938332915306</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03213927149772644</v>
+        <v>0.06538576632738113</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01424253173172474</v>
+        <v>0.2020586878061295</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04628337547183037</v>
+        <v>0.06064892560243607</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3268863260746002</v>
+        <v>0.6157075166702271</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0191385094076395</v>
+        <v>0.3779082298278809</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05786970257759094</v>
+        <v>0.1814360618591309</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1941363215446472</v>
+        <v>0.03176937624812126</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09056119620800018</v>
+        <v>0.2536813914775848</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06740052253007889</v>
+        <v>0.09891623258590698</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0317329615354538</v>
+        <v>0.005357205867767334</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02343046106398106</v>
+        <v>0.4275752902030945</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0413622073829174</v>
+        <v>0.03361564129590988</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1209405511617661</v>
+        <v>0.1244566440582275</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01710517890751362</v>
+        <v>0.2077211737632751</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002535882405936718</v>
+        <v>0.02143550105392933</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0185773316770792</v>
+        <v>0.1829675137996674</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03488427028059959</v>
+        <v>0.211762011051178</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.02508742362260818</v>
+        <v>0.07262442260980606</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.08898938447237015</v>
+        <v>0.03766186907887459</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04087405279278755</v>
+        <v>0.06786217540502548</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06172885745763779</v>
+        <v>0.08993703126907349</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01253431476652622</v>
+        <v>0.09238907694816589</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0281685758382082</v>
+        <v>0.0529664158821106</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01134559605270624</v>
+        <v>0.1129523515701294</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02319658361375332</v>
+        <v>0.420432984828949</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.04431513696908951</v>
+        <v>0.06049917638301849</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.02343316003680229</v>
+        <v>0.04116139560937881</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.01177136600017548</v>
+        <v>0.2028250098228455</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.006786125712096691</v>
+        <v>0.01125919632613659</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.06219349801540375</v>
+        <v>0.05239387974143028</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.09044805914163589</v>
+        <v>0.05801580101251602</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.003515368793159723</v>
+        <v>0.1293248236179352</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01265367679297924</v>
+        <v>0.09946974366903305</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03718750923871994</v>
+        <v>0.3410063982009888</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.02923553623259068</v>
+        <v>0.237552136182785</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01528065651655197</v>
+        <v>0.02604778483510017</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.004519968293607235</v>
+        <v>0.1244807466864586</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.04153406620025635</v>
+        <v>0.1234875246882439</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.09349445253610611</v>
+        <v>0.1238053515553474</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2774709165096283</v>
+        <v>0.1015500649809837</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.02751256711781025</v>
+        <v>0.2887162268161774</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.04709737747907639</v>
+        <v>0.1284831464290619</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03756580874323845</v>
+        <v>0.4819519221782684</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.07277418673038483</v>
+        <v>0.4037996828556061</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.07744827121496201</v>
+        <v>0.01339961402118206</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.02599387057125568</v>
+        <v>0.1286137402057648</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.02855479344725609</v>
+        <v>0.1098943948745728</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.04658710211515427</v>
+        <v>0.1195747256278992</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03300904110074043</v>
+        <v>0.5110382437705994</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.06140578538179398</v>
+        <v>0.09900780767202377</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01602318324148655</v>
+        <v>0.01556209847331047</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.09133403748273849</v>
+        <v>0.7001411914825439</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01116914860904217</v>
+        <v>0.05471356213092804</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.05477908998727798</v>
+        <v>0.1240917593240738</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.02741166576743126</v>
+        <v>0.1857845336198807</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.003017141483724117</v>
+        <v>0.02386963367462158</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.02508083917200565</v>
+        <v>0.1025704145431519</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04445794969797134</v>
+        <v>0.1461613476276398</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.007968166843056679</v>
+        <v>0.04036638885736465</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01005307212471962</v>
+        <v>0.003973588347434998</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.07738437503576279</v>
+        <v>0.3225931823253632</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.05444987863302231</v>
+        <v>0.1118249744176865</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.006814261898398399</v>
+        <v>0.01361206360161304</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01932757161557674</v>
+        <v>0.1507019996643066</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.02908073551952839</v>
+        <v>0.001289915293455124</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.04205448180437088</v>
+        <v>0.1144309192895889</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1905871629714966</v>
+        <v>0.04166167974472046</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.04630936309695244</v>
+        <v>0.2101152539253235</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.04278544336557388</v>
+        <v>0.08324612677097321</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.00790349580347538</v>
+        <v>0.03423600271344185</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01950589753687382</v>
+        <v>0.3484357297420502</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0149007011204958</v>
+        <v>0.1106397286057472</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.04474034160375595</v>
+        <v>0.06021963804960251</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.03240101039409637</v>
+        <v>0.1120852455496788</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.01105220057070255</v>
+        <v>0.01423489674925804</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.06508419662714005</v>
+        <v>0.08411601185798645</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.03121090307831764</v>
+        <v>0.005683379247784615</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.006053047254681587</v>
+        <v>0.008278302848339081</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01250853948295116</v>
+        <v>0.03068285062909126</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.00285418494604528</v>
+        <v>0.1058662384748459</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.02925322949886322</v>
+        <v>0.02151896618306637</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.007653538603335619</v>
+        <v>0.007967917248606682</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.02015135809779167</v>
+        <v>0.06714218109846115</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.1596435159444809</v>
+        <v>0.02419841289520264</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.04230109974741936</v>
+        <v>0.1891376078128815</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.01134089939296246</v>
+        <v>0.3210853338241577</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.03781550005078316</v>
+        <v>0.1052413433790207</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1029697880148888</v>
+        <v>0.3312779366970062</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01702039688825607</v>
+        <v>0.2869322299957275</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.07557576894760132</v>
+        <v>0.0005091093480587006</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.07412710785865784</v>
+        <v>0.1132843270897865</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.04663658887147903</v>
+        <v>0.0289015918970108</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.005908668506890535</v>
+        <v>0.009982012212276459</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0622248686850071</v>
+        <v>0.1095131263136864</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.04097681865096092</v>
+        <v>0.04933265969157219</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02264820225536823</v>
+        <v>0.01807799004018307</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002756861271336675</v>
+        <v>0.008717518299818039</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002337145386263728</v>
+        <v>0.08811993151903152</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.02819210104644299</v>
+        <v>0.01981606334447861</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.01632615365087986</v>
+        <v>0.02983912266790867</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0156110841780901</v>
+        <v>0.05078665912151337</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03269164264202118</v>
+        <v>0.05258342251181602</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1084062159061432</v>
+        <v>0.06581997126340866</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.02195143513381481</v>
+        <v>0.06525804102420807</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0995907261967659</v>
+        <v>0.03605040162801743</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06442427635192871</v>
+        <v>0.04292688518762589</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.04075644910335541</v>
+        <v>0.006206657737493515</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001755779609084129</v>
+        <v>0.02146043255925179</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01055288501083851</v>
+        <v>0.2769201397895813</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.01138241123408079</v>
+        <v>0.3400062322616577</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.001217828597873449</v>
+        <v>0.00399368442595005</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.04627451673150063</v>
+        <v>0.1706490516662598</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.03163500875234604</v>
+        <v>0.06624165177345276</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01070332527160645</v>
+        <v>0.07966575026512146</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.02907108888030052</v>
+        <v>0.1189716160297394</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.024177186191082</v>
+        <v>0.2505857348442078</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.05009216070175171</v>
+        <v>0.09253373742103577</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0015675975009799</v>
+        <v>0.05207045376300812</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.03069238737225533</v>
+        <v>0.06307928264141083</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0142991729080677</v>
+        <v>0.03534375131130219</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1191990152001381</v>
+        <v>0.05362388119101524</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.06496235728263855</v>
+        <v>0.0167803056538105</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.003093154169619083</v>
+        <v>0.0936330258846283</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.05496123433113098</v>
+        <v>0.02031013369560242</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.02349062636494637</v>
+        <v>0.08990039676427841</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.001741299172863364</v>
+        <v>0.01339547522366047</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.02971429377794266</v>
+        <v>0.2697146236896515</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.01675989665091038</v>
+        <v>0.2715970277786255</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0355534553527832</v>
+        <v>0.03752957656979561</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.009056962095201015</v>
+        <v>0.0155789703130722</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.01135700941085815</v>
+        <v>0.0936761274933815</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01328668370842934</v>
+        <v>0.02691470831632614</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0030531648080796</v>
+        <v>0.01739681139588356</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.02788866125047207</v>
+        <v>0.08822967112064362</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.02291486784815788</v>
+        <v>0.007708294317126274</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0110674099996686</v>
+        <v>0.05159703642129898</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.001238303491845727</v>
+        <v>0.1995459496974945</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.009814428165555</v>
+        <v>0.003964226692914963</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02071762457489967</v>
+        <v>0.003215380012989044</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.07306103408336639</v>
+        <v>0.03579636663198471</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01051667146384716</v>
+        <v>0.07488948851823807</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.003896386828273535</v>
+        <v>0.05050967261195183</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.02233793027698994</v>
+        <v>0.2872090935707092</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.07634083181619644</v>
+        <v>0.0177992545068264</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.1029572635889053</v>
+        <v>0.04861695691943169</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.007663208059966564</v>
+        <v>0.07408775389194489</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.01155710872262716</v>
+        <v>0.01095515117049217</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.05964044854044914</v>
+        <v>0.1328796893358231</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.03399433568120003</v>
+        <v>0.01973988860845566</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.001974440179765224</v>
+        <v>0.008579924702644348</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001933761639520526</v>
+        <v>0.06068967282772064</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.00019648447050713</v>
+        <v>0.09006742388010025</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.03943764045834541</v>
+        <v>0.01040581241250038</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.005827436223626137</v>
+        <v>0.004262917675077915</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.02757642976939678</v>
+        <v>0.1021052971482277</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0002360076759941876</v>
+        <v>0.02963905781507492</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.03829634562134743</v>
+        <v>0.01192068867385387</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.07089319080114365</v>
+        <v>0.06045596301555634</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.02616419270634651</v>
+        <v>0.01617066189646721</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.004375333897769451</v>
+        <v>0.1229152381420135</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.03268257901072502</v>
+        <v>0.2433637678623199</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.01578279212117195</v>
+        <v>0.02870853431522846</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.03992024809122086</v>
+        <v>0.1415235698223114</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.01630799286067486</v>
+        <v>0.3561550974845886</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.05139384791254997</v>
+        <v>0.02600657939910889</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.06728055328130722</v>
+        <v>0.0199749544262886</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.04155415669083595</v>
+        <v>0.1046330332756042</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01595191657543182</v>
+        <v>0.2026722729206085</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.002061100676655769</v>
+        <v>0.02984777465462685</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01037608180195093</v>
+        <v>0.1255703568458557</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.05038772523403168</v>
+        <v>0.01440118253231049</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.03266351670026779</v>
+        <v>0.2669208943843842</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.01339152082800865</v>
+        <v>0.08168458938598633</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.08038975298404694</v>
+        <v>0.004744807258248329</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.02848309651017189</v>
+        <v>0.0335567519068718</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.03601043671369553</v>
+        <v>0.1291528940200806</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.03848288580775261</v>
+        <v>0.009970617480576038</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.03119662776589394</v>
+        <v>0.1174429506063461</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.06355136632919312</v>
+        <v>0.4312072396278381</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.1241431534290314</v>
+        <v>0.06266967952251434</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.01405136100947857</v>
+        <v>0.09618517756462097</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.008802760392427444</v>
+        <v>0.1595056653022766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0001171166441054083</v>
+        <v>6.450891669373959e-05</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001237048185430467</v>
+        <v>0.03261193633079529</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001067018674802966</v>
+        <v>0.0148157374933362</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0004314736288506538</v>
+        <v>0.009803183376789093</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003088231314904988</v>
+        <v>0.007461476139724255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006134618306532502</v>
+        <v>0.02278399094939232</v>
       </c>
       <c r="G13" t="n">
-        <v>5.732083081966266e-05</v>
+        <v>0.006443632766604424</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0003735339269042015</v>
+        <v>0.007353258784860373</v>
       </c>
       <c r="I13" t="n">
-        <v>6.168369509396143e-06</v>
+        <v>0.01509168464690447</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000218141358345747</v>
+        <v>0.002680992009118199</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001158298342488706</v>
+        <v>0.03197450190782547</v>
       </c>
       <c r="L13" t="n">
-        <v>1.446435453544836e-05</v>
+        <v>0.02154011465609074</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002432382898405194</v>
+        <v>0.02694818004965782</v>
       </c>
       <c r="N13" t="n">
-        <v>1.148731826106086e-06</v>
+        <v>0.002372649498283863</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0006787022575736046</v>
+        <v>0.0289232861250639</v>
       </c>
       <c r="P13" t="n">
-        <v>7.027263927739114e-05</v>
+        <v>0.00821941252797842</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001337644644081593</v>
+        <v>0.0007522674277424812</v>
       </c>
       <c r="R13" t="n">
-        <v>3.434595419093966e-05</v>
+        <v>0.01967684179544449</v>
       </c>
       <c r="S13" t="n">
-        <v>4.552691098069772e-05</v>
+        <v>0.005132936872541904</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0001019271439872682</v>
+        <v>0.007159569300711155</v>
       </c>
       <c r="U13" t="n">
-        <v>6.771088374080136e-05</v>
+        <v>0.003238328266888857</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0001876055321190506</v>
+        <v>0.001620011869817972</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0001159649837063625</v>
+        <v>0.004558240994811058</v>
       </c>
       <c r="X13" t="n">
-        <v>6.212814696482383e-06</v>
+        <v>0.002088551176711917</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.402502832410391e-05</v>
+        <v>0.006049223244190216</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001151540491264313</v>
+        <v>0.00212807534262538</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.298263618489727e-05</v>
+        <v>0.003804826410487294</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.940578658832237e-05</v>
+        <v>0.004214445129036903</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.087259988707956e-05</v>
+        <v>0.0008902432164177299</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.072104638908058e-05</v>
+        <v>0.007190936245024204</v>
       </c>
       <c r="AE13" t="n">
-        <v>9.967650839826092e-05</v>
+        <v>0.007986921817064285</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.171065903501585e-05</v>
+        <v>0.01047243736684322</v>
       </c>
       <c r="AG13" t="n">
-        <v>9.97924325929489e-06</v>
+        <v>0.01429695636034012</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.886056452349294e-05</v>
+        <v>0.003449574811384082</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.00010916428436758</v>
+        <v>0.02384053356945515</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.179049134720117e-05</v>
+        <v>0.0003467149799689651</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0002299183834111318</v>
+        <v>0.003320765215903521</v>
       </c>
       <c r="AL13" t="n">
-        <v>8.248706581071019e-05</v>
+        <v>0.00529630109667778</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.746865382301621e-05</v>
+        <v>0.0006982332561165094</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.815226803766564e-06</v>
+        <v>0.002923974767327309</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.595397280761972e-05</v>
+        <v>0.007218272890895605</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0001731083902996033</v>
+        <v>0.002600452397018671</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.989786248188466e-05</v>
+        <v>0.0002487649326212704</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001092257371055894</v>
+        <v>0.007076353300362825</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0001408308889949694</v>
+        <v>0.002587185706943274</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.921795021393336e-05</v>
+        <v>0.005858135409653187</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.000686386541929096</v>
+        <v>0.03017770126461983</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0001776876015355811</v>
+        <v>0.009323012083768845</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.172630749759264e-05</v>
+        <v>0.009552048519253731</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0002155125694116578</v>
+        <v>0.02012882381677628</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0002793985768221319</v>
+        <v>0.02282928489148617</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.236093708546832e-05</v>
+        <v>0.002349377376958728</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0001498496276326478</v>
+        <v>0.008714592084288597</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0001002957942546345</v>
+        <v>0.002513691317290068</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.35571967298165e-05</v>
+        <v>0.005796131677925587</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.000255537626799196</v>
+        <v>0.00336635927669704</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0003351273480802774</v>
+        <v>0.01164150424301624</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.310872489237227e-05</v>
+        <v>0.00426699873059988</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.064659050432965e-05</v>
+        <v>0.01656481251120567</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0001000667907646857</v>
+        <v>0.003680491354316473</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001175436555058695</v>
+        <v>0.007365399040281773</v>
       </c>
       <c r="BJ13" t="n">
-        <v>5.158224666956812e-05</v>
+        <v>0.001961924834176898</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.267237090971321e-05</v>
+        <v>0.009988238103687763</v>
       </c>
       <c r="BL13" t="n">
-        <v>8.67922353791073e-05</v>
+        <v>0.0002412336179986596</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0001645397569518536</v>
+        <v>0.01067366451025009</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0001411358680343255</v>
+        <v>0.005735649261623621</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.725633723661304e-05</v>
+        <v>0.002897663973271847</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.047788388561457e-05</v>
+        <v>0.005562174133956432</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.611511419876479e-05</v>
+        <v>0.004375656135380268</v>
       </c>
       <c r="BR13" t="n">
-        <v>7.142277172533795e-05</v>
+        <v>0.004331436473876238</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.146472828229889e-05</v>
+        <v>0.001706309500150383</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001771178212948143</v>
+        <v>0.0026514264754951</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.812959403148852e-05</v>
+        <v>0.002418969292193651</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0004195033689029515</v>
+        <v>0.01717999763786793</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0001338043803116307</v>
+        <v>0.004137756302952766</v>
       </c>
       <c r="BX13" t="n">
-        <v>1.615720975678414e-05</v>
+        <v>0.003528164932504296</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.103412594413385e-05</v>
+        <v>0.004085303284227848</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0001687228505034</v>
+        <v>0.00911472924053669</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.878321356547531e-05</v>
+        <v>0.01079789269715548</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.570114080910571e-05</v>
+        <v>0.001182300271466374</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.579787855618633e-05</v>
+        <v>0.005691076628863811</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.315476326155476e-05</v>
+        <v>0.0002508106990717351</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0002360898215556517</v>
+        <v>0.01107136625796556</v>
       </c>
       <c r="CF13" t="n">
-        <v>9.1514055384323e-05</v>
+        <v>0.005064566619694233</v>
       </c>
       <c r="CG13" t="n">
-        <v>7.011259731370956e-05</v>
+        <v>0.003586011473089457</v>
       </c>
       <c r="CH13" t="n">
-        <v>5.832851456943899e-05</v>
+        <v>0.0006316102808341384</v>
       </c>
       <c r="CI13" t="n">
-        <v>4.306236587581225e-05</v>
+        <v>0.00453645084053278</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.251956074265763e-05</v>
+        <v>0.0002871012839023024</v>
       </c>
       <c r="CK13" t="n">
-        <v>8.669171074870974e-05</v>
+        <v>0.0006858757697045803</v>
       </c>
       <c r="CL13" t="n">
-        <v>6.106386717874557e-05</v>
+        <v>0.002086003310978413</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0002791569568216801</v>
+        <v>0.004805959761142731</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0001084002433344722</v>
+        <v>0.003412917722016573</v>
       </c>
       <c r="CO13" t="n">
-        <v>5.603586487268331e-06</v>
+        <v>0.009644506499171257</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0002151614025933668</v>
+        <v>0.0124169671908021</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0001465432142140344</v>
+        <v>0.005693668499588966</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0003277101495768875</v>
+        <v>0.002700289944186807</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002248292585136369</v>
+        <v>0.006489779334515333</v>
       </c>
       <c r="CT13" t="n">
-        <v>6.952360126888379e-05</v>
+        <v>0.002155381953343749</v>
       </c>
       <c r="CU13" t="n">
-        <v>5.762340151704848e-05</v>
+        <v>0.006497327238321304</v>
       </c>
       <c r="CV13" t="n">
-        <v>3.773729258682579e-05</v>
+        <v>0.002491294406354427</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002261948538944125</v>
+        <v>0.008660925552248955</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001248415355803445</v>
+        <v>0.006778721697628498</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.000122028446639888</v>
+        <v>0.00521854730322957</v>
       </c>
       <c r="CZ13" t="n">
-        <v>5.122640504851006e-05</v>
+        <v>0.0007996554486453533</v>
       </c>
       <c r="DA13" t="n">
-        <v>6.338359526125714e-05</v>
+        <v>0.007722056936472654</v>
       </c>
       <c r="DB13" t="n">
-        <v>5.995520405122079e-05</v>
+        <v>0.001735553843900561</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001494045718573034</v>
+        <v>0.0007644675788469613</v>
       </c>
       <c r="DD13" t="n">
-        <v>5.021639663027599e-05</v>
+        <v>0.003057485911995173</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001370056997984648</v>
+        <v>0.0008778998162597418</v>
       </c>
       <c r="DF13" t="n">
-        <v>6.6605512984097e-05</v>
+        <v>0.01817023567855358</v>
       </c>
       <c r="DG13" t="n">
-        <v>4.331540822022362e-06</v>
+        <v>0.01512507721781731</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004261558351572603</v>
+        <v>0.0001692943624220788</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0004867747484240681</v>
+        <v>0.005357318092137575</v>
       </c>
       <c r="DJ13" t="n">
-        <v>8.768583938945085e-05</v>
+        <v>0.01782485283911228</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0001551551395095885</v>
+        <v>0.005678699351847172</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0001668906043050811</v>
+        <v>0.009497806429862976</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0001775909477146342</v>
+        <v>0.0005609606159850955</v>
       </c>
       <c r="DN13" t="n">
-        <v>7.034532609395683e-05</v>
+        <v>0.002195702865719795</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0001335168199148029</v>
+        <v>0.008114300668239594</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.827017154544592e-05</v>
+        <v>0.004048534668982029</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0001425681984983385</v>
+        <v>0.008565829135477543</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.019356128992513e-05</v>
+        <v>0.0001300816657021642</v>
       </c>
       <c r="DS13" t="n">
-        <v>9.399465488968417e-05</v>
+        <v>0.004869308788329363</v>
       </c>
       <c r="DT13" t="n">
-        <v>5.445639544632286e-05</v>
+        <v>0.002665768377482891</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0001296676200581715</v>
+        <v>0.01015174202620983</v>
       </c>
       <c r="DV13" t="n">
-        <v>5.699021494365297e-05</v>
+        <v>0.004803964402526617</v>
       </c>
       <c r="DW13" t="n">
-        <v>3.70309135178104e-06</v>
+        <v>0.0006172927096486092</v>
       </c>
       <c r="DX13" t="n">
-        <v>5.746578608523123e-05</v>
+        <v>0.008592592552304268</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0001308555947616696</v>
+        <v>0.01233669370412827</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.62122048297897e-05</v>
+        <v>0.002585174050182104</v>
       </c>
       <c r="EA13" t="n">
-        <v>7.160037057474256e-05</v>
+        <v>0.007061610464006662</v>
       </c>
       <c r="EB13" t="n">
-        <v>4.216229353914969e-05</v>
+        <v>0.003841590136289597</v>
       </c>
       <c r="EC13" t="n">
-        <v>9.528168448014185e-05</v>
+        <v>0.012037243694067</v>
       </c>
       <c r="ED13" t="n">
-        <v>2.266719457111321e-05</v>
+        <v>0.005447434261441231</v>
       </c>
       <c r="EE13" t="n">
-        <v>8.482078555971384e-05</v>
+        <v>0.01784889400005341</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002097113756462932</v>
+        <v>0.000280670530628413</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0002718578616622835</v>
+        <v>0.001828609616495669</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0001542687678011134</v>
+        <v>0.0006986712105572224</v>
       </c>
       <c r="EI13" t="n">
-        <v>7.639691466465592e-05</v>
+        <v>0.01022890489548445</v>
       </c>
       <c r="EJ13" t="n">
-        <v>6.392368231900036e-05</v>
+        <v>0.0005076772067695856</v>
       </c>
       <c r="EK13" t="n">
-        <v>5.531381611945108e-05</v>
+        <v>0.0009288747096434236</v>
       </c>
       <c r="EL13" t="n">
-        <v>4.676752723753452e-05</v>
+        <v>0.0029989427421242</v>
       </c>
       <c r="EM13" t="n">
-        <v>3.519750316627324e-05</v>
+        <v>0.003488517832010984</v>
       </c>
       <c r="EN13" t="n">
-        <v>1.894168417493347e-05</v>
+        <v>0.01030332408845425</v>
       </c>
       <c r="EO13" t="n">
-        <v>4.368257577880286e-05</v>
+        <v>0.002965949941426516</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001042201110976748</v>
+        <v>0.008361048996448517</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001334457192569971</v>
+        <v>0.002655017655342817</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001554163900436834</v>
+        <v>0.005249736830592155</v>
       </c>
       <c r="ES13" t="n">
-        <v>6.048800423741341e-05</v>
+        <v>0.006754779256880283</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0001966887502931058</v>
+        <v>0.009398192167282104</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0001422098866896704</v>
+        <v>0.002194348722696304</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0002619430888444185</v>
+        <v>0.000391942507121712</v>
       </c>
       <c r="EW13" t="n">
-        <v>5.336994217941537e-05</v>
+        <v>0.001917108776979148</v>
       </c>
       <c r="EX13" t="n">
-        <v>5.828135181218386e-05</v>
+        <v>0.0007506835390813649</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0002111710928147659</v>
+        <v>0.01197544857859612</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001042448639054783</v>
+        <v>0.003356171771883965</v>
       </c>
       <c r="FA13" t="n">
-        <v>5.717070598620921e-05</v>
+        <v>0.005877763032913208</v>
       </c>
       <c r="FB13" t="n">
-        <v>4.964388426742516e-05</v>
+        <v>0.000903288833796978</v>
       </c>
       <c r="FC13" t="n">
-        <v>4.557760621537454e-05</v>
+        <v>0.005699330009520054</v>
       </c>
       <c r="FD13" t="n">
-        <v>8.314280421473086e-05</v>
+        <v>0.0009121020557358861</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0001354932901449502</v>
+        <v>0.000794422288890928</v>
       </c>
       <c r="FF13" t="n">
-        <v>7.210381590994075e-05</v>
+        <v>0.004285064060240984</v>
       </c>
       <c r="FG13" t="n">
-        <v>6.569868128281087e-05</v>
+        <v>0.004284283146262169</v>
       </c>
       <c r="FH13" t="n">
-        <v>1.130351756728487e-05</v>
+        <v>0.0002538659609854221</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000204478099476546</v>
+        <v>0.00685869250446558</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0001143027839134447</v>
+        <v>0.00294514512643218</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001065230462700129</v>
+        <v>5.642138421535492e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0001495410542702302</v>
+        <v>0.01103018037974834</v>
       </c>
       <c r="FM13" t="n">
-        <v>6.078604201320559e-06</v>
+        <v>0.003921811934560537</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001022393407765776</v>
+        <v>0.00890703871846199</v>
       </c>
       <c r="FO13" t="n">
-        <v>7.502325752284378e-05</v>
+        <v>0.02132498286664486</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0001868995896074921</v>
+        <v>0.0003418305423110723</v>
       </c>
       <c r="FQ13" t="n">
-        <v>2.495248190825805e-05</v>
+        <v>0.003219974227249622</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0002367871784372255</v>
+        <v>0.00110035203397274</v>
       </c>
       <c r="FS13" t="n">
-        <v>3.807336543104611e-05</v>
+        <v>0.003244993276894093</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0001447061513317749</v>
+        <v>0.008134212344884872</v>
       </c>
       <c r="FU13" t="n">
-        <v>6.609542469959706e-05</v>
+        <v>0.003486283589154482</v>
       </c>
       <c r="FV13" t="n">
-        <v>3.823870792984962e-05</v>
+        <v>0.00459055881947279</v>
       </c>
       <c r="FW13" t="n">
-        <v>1.530443114461377e-06</v>
+        <v>0.02384127303957939</v>
       </c>
       <c r="FX13" t="n">
-        <v>1.691376564849634e-05</v>
+        <v>0.002700160490348935</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0002291093696840107</v>
+        <v>0.001432353863492608</v>
       </c>
       <c r="FZ13" t="n">
-        <v>9.376340312883258e-05</v>
+        <v>0.0009813362266868353</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0001315207919105887</v>
+        <v>0.01584786176681519</v>
       </c>
       <c r="GB13" t="n">
-        <v>4.661342245526612e-05</v>
+        <v>0.00122493936214596</v>
       </c>
       <c r="GC13" t="n">
-        <v>4.06546205340419e-05</v>
+        <v>0.01546382717788219</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0001466636313125491</v>
+        <v>0.007297397591173649</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002653019037097692</v>
+        <v>0.005408594384789467</v>
       </c>
       <c r="GF13" t="n">
-        <v>3.391452992218547e-05</v>
+        <v>0.002502246294170618</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.000152897642692551</v>
+        <v>0.001661688787862659</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0001249665656359866</v>
+        <v>8.527305972449994e-09</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003868176136165857</v>
+        <v>1.218767042843183e-08</v>
       </c>
       <c r="C14" t="n">
-        <v>9.836276876740158e-05</v>
+        <v>4.470361858466276e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006247262936085463</v>
+        <v>3.893769306984041e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001497651799581945</v>
+        <v>3.373014312302303e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004911727737635374</v>
+        <v>7.250302580530388e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001788444060366601</v>
+        <v>8.725774547357901e-10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005417066859081388</v>
+        <v>6.757512771571328e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>2.488811878720298e-05</v>
+        <v>5.921224399685343e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>3.765890141949058e-05</v>
+        <v>1.022926010563197e-08</v>
       </c>
       <c r="K14" t="n">
-        <v>0.003379252506420016</v>
+        <v>1.366785795653414e-08</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0006403201259672642</v>
+        <v>5.017251059058481e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>3.880217991536483e-05</v>
+        <v>4.066126990664998e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0009862065780907869</v>
+        <v>3.56796858724806e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006737833609804511</v>
+        <v>6.055218548794983e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001403860806021839</v>
+        <v>2.029962448135691e-10</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001442421053070575</v>
+        <v>7.392531919947487e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>3.168168041156605e-05</v>
+        <v>4.905283401690497e-10</v>
       </c>
       <c r="S14" t="n">
-        <v>3.705840208567679e-05</v>
+        <v>2.287760425545571e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0004803587798960507</v>
+        <v>1.51178636276228e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>7.85202719271183e-05</v>
+        <v>9.306432846578616e-10</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0004044164670631289</v>
+        <v>3.13256642847648e-10</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0007015583105385303</v>
+        <v>1.083836465021193e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000141356562380679</v>
+        <v>1.545450989404173e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.002524166135117e-05</v>
+        <v>8.698752829161549e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0006655477918684483</v>
+        <v>4.277482368308938e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001770443341229111</v>
+        <v>2.842293955751529e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0002044109569396824</v>
+        <v>1.035204366672815e-09</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.011200745590031e-06</v>
+        <v>1.918087910723898e-09</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001038252958096564</v>
+        <v>2.951226152347886e-09</v>
       </c>
       <c r="AE14" t="n">
-        <v>5.316311217029579e-05</v>
+        <v>1.934027160643836e-09</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0002557969419285655</v>
+        <v>8.642021542826228e-10</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.943587504792958e-05</v>
+        <v>1.900652080166765e-09</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.297542520565912e-05</v>
+        <v>1.091496115712687e-09</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001972133904928342</v>
+        <v>1.387904569050136e-09</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.000339683931088075</v>
+        <v>3.522835134717184e-09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0006539238383993506</v>
+        <v>4.442531231774183e-09</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0004238486289978027</v>
+        <v>1.190225251690435e-09</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001188211317639798</v>
+        <v>4.358383876024163e-09</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.100615165545605e-05</v>
+        <v>1.640637070643436e-09</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0004385246429592371</v>
+        <v>1.65822647280045e-10</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.000375264004105702</v>
+        <v>6.08311290228869e-10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.067332727368921e-06</v>
+        <v>6.246446693225494e-10</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001436168095096946</v>
+        <v>4.439867362648897e-10</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.912053504493088e-05</v>
+        <v>1.297188051418985e-10</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.355700391693972e-05</v>
+        <v>8.635766768350095e-09</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.002568322466686368</v>
+        <v>4.027113087445855e-10</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0003314708592370152</v>
+        <v>4.023245736561876e-09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0002425499260425568</v>
+        <v>2.210751581799286e-09</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0008904673741199076</v>
+        <v>8.144526830733412e-09</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0003942878101952374</v>
+        <v>8.980642340894462e-10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0002780619543045759</v>
+        <v>1.138777294684701e-09</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001000538759399205</v>
+        <v>3.306121487689495e-10</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.740870645036921e-05</v>
+        <v>6.547458131223038e-10</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0004744438629131764</v>
+        <v>2.469703108687327e-09</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.000923574436455965</v>
+        <v>7.10667702463752e-09</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0005980835994705558</v>
+        <v>9.754663743422043e-11</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0001395020808558911</v>
+        <v>2.399838994193715e-09</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0006391920032911003</v>
+        <v>8.632839332278763e-09</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0003957330191042274</v>
+        <v>5.178000694883167e-09</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0003678200591821223</v>
+        <v>7.072656349471629e-10</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002154509274987504</v>
+        <v>2.211251182160368e-09</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0001134665144491009</v>
+        <v>5.071209230322893e-09</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0003355027001816779</v>
+        <v>3.869925491173376e-10</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0007074463064782321</v>
+        <v>8.552655250682051e-10</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0003579319745767862</v>
+        <v>2.843611734970608e-10</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0001654216030146927</v>
+        <v>8.88635887097422e-10</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0004059695638716221</v>
+        <v>6.967128540757983e-10</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0002020283136516809</v>
+        <v>1.664834659020897e-10</v>
       </c>
       <c r="BR14" t="n">
-        <v>4.065080429427326e-05</v>
+        <v>1.621337397672562e-09</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001159036037279293</v>
+        <v>1.237436930701108e-09</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0001726977934595197</v>
+        <v>1.686278894297288e-09</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.891526234336197e-05</v>
+        <v>5.883903142489544e-09</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.001568268868140876</v>
+        <v>2.103654750396089e-10</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0002494979707989842</v>
+        <v>1.541981209385312e-09</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0001440394553355873</v>
+        <v>2.404387522414453e-10</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0004767325590364635</v>
+        <v>6.096863014448672e-10</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001882490905700251</v>
+        <v>8.163936193739119e-10</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001822855265345424</v>
+        <v>1.258784187996298e-09</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.000142455828608945</v>
+        <v>2.130914333875467e-09</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0001074076644727029</v>
+        <v>1.199488730563303e-09</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001107070711441338</v>
+        <v>1.471523458640434e-09</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.000606117770075798</v>
+        <v>2.97524760384249e-09</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001425347290933132</v>
+        <v>4.269915809818059e-10</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001071679871529341</v>
+        <v>1.487847733905312e-09</v>
       </c>
       <c r="CH14" t="n">
-        <v>3.936531720682979e-05</v>
+        <v>1.629515189449648e-09</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.257724306924501e-05</v>
+        <v>2.654119590772552e-09</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001754867262206972</v>
+        <v>3.686464744578899e-10</v>
       </c>
       <c r="CK14" t="n">
-        <v>9.86686791293323e-05</v>
+        <v>1.039489050391751e-09</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.778869409463368e-05</v>
+        <v>1.083545808633346e-09</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0008421585662290454</v>
+        <v>1.598829069138219e-09</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0005413807230070233</v>
+        <v>7.108089672414053e-10</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0002414977498119697</v>
+        <v>2.992480041541512e-09</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0001831045374274254</v>
+        <v>1.353840706208587e-09</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0004864432848989964</v>
+        <v>2.704519275198436e-09</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0003917122085113078</v>
+        <v>2.10938644329417e-09</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0006204526289366186</v>
+        <v>9.887630714189299e-10</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0004868296382483095</v>
+        <v>1.596425103222998e-09</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001204040090669878</v>
+        <v>2.136700594235208e-09</v>
       </c>
       <c r="CV14" t="n">
-        <v>9.1767986305058e-05</v>
+        <v>1.009202388324582e-09</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0004913857555948198</v>
+        <v>2.815180089044134e-09</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0002396461204625666</v>
+        <v>3.901781120418946e-10</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0002956481475848705</v>
+        <v>1.582355690921133e-09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>7.333753455895931e-05</v>
+        <v>1.1331506843959e-09</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.680675581563264e-05</v>
+        <v>2.451677971748722e-09</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001426751259714365</v>
+        <v>3.510977064635767e-10</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001769336085999385</v>
+        <v>1.95389082691122e-09</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.290769771207124e-05</v>
+        <v>1.233887325646776e-09</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0003477345744613558</v>
+        <v>1.054921927590158e-09</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0006204997189342976</v>
+        <v>5.21578469303563e-09</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.276839611819014e-05</v>
+        <v>4.80699258176287e-09</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001365111558698118</v>
+        <v>1.737832544534967e-09</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.000622734718490392</v>
+        <v>4.721417035113973e-09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0002375525946263224</v>
+        <v>1.567962981674498e-09</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.000241104542510584</v>
+        <v>3.127649694789625e-09</v>
       </c>
       <c r="DL14" t="n">
-        <v>9.795719961402938e-05</v>
+        <v>8.962319775207561e-11</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001864591467892751</v>
+        <v>3.260355985190699e-09</v>
       </c>
       <c r="DN14" t="n">
-        <v>5.405749834608287e-05</v>
+        <v>2.564585210862447e-09</v>
       </c>
       <c r="DO14" t="n">
-        <v>6.303676491370425e-05</v>
+        <v>3.750465271679104e-09</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.000366669031791389</v>
+        <v>1.681469408154612e-09</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0002672391710802913</v>
+        <v>2.905604645775384e-09</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0002440823154756799</v>
+        <v>1.077398170679089e-09</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0002537761174608022</v>
+        <v>1.078968359102817e-09</v>
       </c>
       <c r="DT14" t="n">
-        <v>4.942637679050677e-05</v>
+        <v>2.196136161813911e-09</v>
       </c>
       <c r="DU14" t="n">
-        <v>3.059209848288447e-05</v>
+        <v>2.084779682220983e-09</v>
       </c>
       <c r="DV14" t="n">
-        <v>3.024833495146595e-05</v>
+        <v>1.683725603385255e-09</v>
       </c>
       <c r="DW14" t="n">
-        <v>3.93405971408356e-05</v>
+        <v>2.390005970909215e-09</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0004156583163421601</v>
+        <v>9.847577198129898e-10</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002078880788758397</v>
+        <v>1.988020859045037e-09</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6.727030267938972e-06</v>
+        <v>3.792289815507388e-10</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003609322884585708</v>
+        <v>6.907267646738546e-09</v>
       </c>
       <c r="EB14" t="n">
-        <v>4.631440242519602e-05</v>
+        <v>1.703888918846985e-09</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0001002766075544059</v>
+        <v>2.056040893094746e-09</v>
       </c>
       <c r="ED14" t="n">
-        <v>3.576544258976355e-05</v>
+        <v>1.998369913991382e-09</v>
       </c>
       <c r="EE14" t="n">
-        <v>2.640197271830402e-05</v>
+        <v>1.621787926175955e-09</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0003832211659755558</v>
+        <v>1.868452947917376e-09</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0006472521345131099</v>
+        <v>8.490261826921142e-10</v>
       </c>
       <c r="EH14" t="n">
-        <v>3.540120451361872e-05</v>
+        <v>1.830643636679952e-09</v>
       </c>
       <c r="EI14" t="n">
-        <v>1.282730227103457e-05</v>
+        <v>1.303735452928834e-10</v>
       </c>
       <c r="EJ14" t="n">
-        <v>4.619421088136733e-05</v>
+        <v>2.762244599718855e-11</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.159756695618853e-05</v>
+        <v>1.999149068510064e-09</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001016468595480546</v>
+        <v>5.6489907196422e-10</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0001358881127089262</v>
+        <v>8.586783506459028e-10</v>
       </c>
       <c r="EN14" t="n">
-        <v>3.283403202658519e-05</v>
+        <v>9.411632584388485e-10</v>
       </c>
       <c r="EO14" t="n">
-        <v>9.330290777143091e-05</v>
+        <v>4.363666095130725e-10</v>
       </c>
       <c r="EP14" t="n">
-        <v>5.421113746706396e-05</v>
+        <v>2.360510675813998e-09</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0004607366281561553</v>
+        <v>4.554902011122408e-10</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0003623258089646697</v>
+        <v>4.297081857007612e-10</v>
       </c>
       <c r="ES14" t="n">
-        <v>2.883210800064262e-05</v>
+        <v>2.629421569366741e-09</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.000149862389662303</v>
+        <v>2.55302468055163e-09</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0002211350365541875</v>
+        <v>1.358586576571952e-10</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0004465146630536765</v>
+        <v>1.573734698112617e-09</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0003069215454161167</v>
+        <v>3.777840262841892e-09</v>
       </c>
       <c r="EX14" t="n">
-        <v>6.902911991346627e-05</v>
+        <v>1.53182933004814e-09</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0005298923351801932</v>
+        <v>3.589375463519673e-09</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0001857876632129773</v>
+        <v>9.495597363962105e-11</v>
       </c>
       <c r="FA14" t="n">
-        <v>5.650417369906791e-05</v>
+        <v>1.886355294189457e-09</v>
       </c>
       <c r="FB14" t="n">
-        <v>1.515471922175493e-06</v>
+        <v>1.792189618932127e-09</v>
       </c>
       <c r="FC14" t="n">
-        <v>8.809546125121415e-05</v>
+        <v>2.233726759115484e-09</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0002072813222184777</v>
+        <v>1.620055756212935e-10</v>
       </c>
       <c r="FE14" t="n">
-        <v>8.43853922560811e-05</v>
+        <v>2.095555950987205e-09</v>
       </c>
       <c r="FF14" t="n">
-        <v>4.25798752985429e-05</v>
+        <v>5.860369967081169e-10</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001139033847721294</v>
+        <v>6.228823568044106e-10</v>
       </c>
       <c r="FH14" t="n">
-        <v>2.313108052476309e-05</v>
+        <v>2.718750558017291e-09</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0003852691152133048</v>
+        <v>3.458699993075243e-09</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.000282667635474354</v>
+        <v>1.18027521089914e-09</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0003843445447273552</v>
+        <v>3.983597451906462e-09</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0001782843755790964</v>
+        <v>2.387896325117822e-09</v>
       </c>
       <c r="FM14" t="n">
-        <v>9.614053124096245e-05</v>
+        <v>1.184947140409065e-10</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0001063381205312908</v>
+        <v>3.316011465415158e-09</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0002776558394543827</v>
+        <v>6.428504395472601e-10</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0003997875028289855</v>
+        <v>3.961002192909291e-09</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0005327918916009367</v>
+        <v>4.925776675435145e-09</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0004517521883826703</v>
+        <v>8.516439997663383e-09</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0001747551141306758</v>
+        <v>2.819688926791741e-09</v>
       </c>
       <c r="FT14" t="n">
-        <v>8.574272214900702e-06</v>
+        <v>2.20360307778833e-09</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0001349357335129753</v>
+        <v>1.446125552639899e-09</v>
       </c>
       <c r="FV14" t="n">
-        <v>9.410592610947788e-06</v>
+        <v>4.024406141667214e-09</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001590175379533321</v>
+        <v>1.905616109354469e-09</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0001024590310407802</v>
+        <v>2.826948675149765e-09</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0005127167096361518</v>
+        <v>2.010105193406275e-09</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001963107060873881</v>
+        <v>3.558519257040871e-09</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0001022866053972393</v>
+        <v>3.77091380343586e-09</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001255335082532838</v>
+        <v>6.384114348279013e-10</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0002646413340698928</v>
+        <v>5.832595739718727e-09</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0006028456846252084</v>
+        <v>1.552571182728002e-09</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.000551949255168438</v>
+        <v>1.552900474877106e-09</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0002710141707211733</v>
+        <v>1.274005456686211e-09</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0002056869125226513</v>
+        <v>2.384840103175634e-09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.408277502283454e-05</v>
+        <v>5.475449142977595e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001144577981904149</v>
+        <v>0.007209243252873421</v>
       </c>
       <c r="C15" t="n">
-        <v>9.008905180962756e-05</v>
+        <v>0.0004114933544769883</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006947661750018597</v>
+        <v>0.00597032718360424</v>
       </c>
       <c r="E15" t="n">
-        <v>5.069307735539041e-05</v>
+        <v>0.00146239111199975</v>
       </c>
       <c r="F15" t="n">
-        <v>4.394125426188111e-06</v>
+        <v>0.008973400108516216</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001045923636411317</v>
+        <v>0.002945741172879934</v>
       </c>
       <c r="H15" t="n">
-        <v>6.168438994791359e-05</v>
+        <v>0.003712129546329379</v>
       </c>
       <c r="I15" t="n">
-        <v>9.638263145461679e-05</v>
+        <v>0.002952216425910592</v>
       </c>
       <c r="J15" t="n">
-        <v>6.067461072234437e-05</v>
+        <v>0.0004596076032612473</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0009694110485725105</v>
+        <v>0.008345644921064377</v>
       </c>
       <c r="L15" t="n">
-        <v>8.279030225821771e-06</v>
+        <v>0.001920708455145359</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000673311878927052</v>
+        <v>0.007582433521747589</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0001623217685846612</v>
+        <v>0.002662214683368802</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0001244851591764018</v>
+        <v>0.009736546315252781</v>
       </c>
       <c r="P15" t="n">
-        <v>6.872281664982438e-05</v>
+        <v>0.001449732226319611</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001188285095850006</v>
+        <v>0.003032924374565482</v>
       </c>
       <c r="R15" t="n">
-        <v>3.286716673756018e-05</v>
+        <v>0.001430449308827519</v>
       </c>
       <c r="S15" t="n">
-        <v>9.661237709224224e-05</v>
+        <v>0.0001840378681663424</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001157778679043986</v>
+        <v>0.0002259340835735202</v>
       </c>
       <c r="U15" t="n">
-        <v>4.814170461031608e-05</v>
+        <v>0.0008476085495203733</v>
       </c>
       <c r="V15" t="n">
-        <v>6.986539665376768e-05</v>
+        <v>0.0006773952627554536</v>
       </c>
       <c r="W15" t="n">
-        <v>5.002252510166727e-05</v>
+        <v>0.0004590578028000891</v>
       </c>
       <c r="X15" t="n">
-        <v>6.906525959493592e-05</v>
+        <v>0.001579598872922361</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.224587120115757e-05</v>
+        <v>0.001133210957050323</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0001025473902700469</v>
+        <v>0.001453119795769453</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.509566785302013e-05</v>
+        <v>0.0004019976768177003</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0001440609194105491</v>
+        <v>0.000633592251688242</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0002688619133550674</v>
+        <v>0.0007083053351379931</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.776504152279813e-05</v>
+        <v>0.001352379214949906</v>
       </c>
       <c r="AE15" t="n">
-        <v>5.474582212627865e-05</v>
+        <v>0.0009975482244044542</v>
       </c>
       <c r="AF15" t="n">
-        <v>7.280113641172647e-05</v>
+        <v>0.0001455873134545982</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.778182195266709e-06</v>
+        <v>0.00310291675850749</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.581076740985736e-05</v>
+        <v>0.0002023826236836612</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.272869889769936e-06</v>
+        <v>0.003621244570240378</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.876088936114684e-05</v>
+        <v>0.000107829189801123</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.004842488327995e-06</v>
+        <v>0.0005219306331127882</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0001026326499413699</v>
+        <v>0.001017460133880377</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.369584737811238e-05</v>
+        <v>0.001233381452038884</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.904312375700101e-05</v>
+        <v>0.001204732805490494</v>
       </c>
       <c r="AO15" t="n">
-        <v>9.567470988258719e-05</v>
+        <v>0.0001519261277280748</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.688267214689404e-05</v>
+        <v>0.0003320709511172026</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.107147343456745e-05</v>
+        <v>0.0001120546949096024</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.750701216631569e-05</v>
+        <v>0.0005789260612800717</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.97563276742585e-05</v>
+        <v>0.0007751616649329662</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0001280878495890647</v>
+        <v>0.001206497428938746</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0007529962458647788</v>
+        <v>0.00335434777662158</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.000147232145536691</v>
+        <v>0.001643773051910102</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0002528811746742576</v>
+        <v>0.002658159472048283</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.092340067378245e-06</v>
+        <v>0.006672651972621679</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.307084110332653e-05</v>
+        <v>0.00515531562268734</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.540968464221805e-06</v>
+        <v>0.0001600277610123158</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.049924660241231e-05</v>
+        <v>0.0009359533432871103</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.778729362442391e-06</v>
+        <v>0.0005625407793559134</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.900441414676607e-05</v>
+        <v>0.0002489418548066169</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0001844162325141951</v>
+        <v>0.002375805051997304</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0002372921298956499</v>
+        <v>0.001409887801855803</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0001060095382854342</v>
+        <v>0.00110958400182426</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.390039485879242e-05</v>
+        <v>0.004060546401888132</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0001248042972292751</v>
+        <v>0.001664391485974193</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0001006188394967467</v>
+        <v>0.0009267404675483704</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.555040014674887e-05</v>
+        <v>0.003954239655286074</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.926192948711105e-05</v>
+        <v>0.001278188545256853</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0001037265319610015</v>
+        <v>0.0002286445087520406</v>
       </c>
       <c r="BM15" t="n">
-        <v>7.688572077313438e-05</v>
+        <v>0.0002592967357486486</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0001340703893220052</v>
+        <v>6.683371611870825e-05</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.504306939954404e-05</v>
+        <v>0.001899833790957928</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0001828768581617624</v>
+        <v>5.309397238306701e-06</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.355937951710075e-05</v>
+        <v>0.001466049114242196</v>
       </c>
       <c r="BR15" t="n">
-        <v>7.222055864986032e-05</v>
+        <v>0.0002833491307683289</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.513916453812271e-05</v>
+        <v>0.001849440857768059</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.354720244416967e-05</v>
+        <v>0.001147749368101358</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.321197285316885e-05</v>
+        <v>0.0005301135824993253</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0003723172703757882</v>
+        <v>0.001767890062183142</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.58103487896733e-05</v>
+        <v>0.0008477560477331281</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0001467454567318782</v>
+        <v>0.002416204195469618</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.746939031174406e-05</v>
+        <v>0.001816174597479403</v>
       </c>
       <c r="BZ15" t="n">
-        <v>8.03125585662201e-05</v>
+        <v>0.002727333921939135</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.184370507369749e-05</v>
+        <v>0.001540685771033168</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.852493344107643e-05</v>
+        <v>8.338101906701922e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.956523116561584e-05</v>
+        <v>0.000819340581074357</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.779551348590758e-05</v>
+        <v>0.0002332021831534803</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0002104489394696429</v>
+        <v>0.002096600830554962</v>
       </c>
       <c r="CF15" t="n">
-        <v>4.779360097018071e-05</v>
+        <v>9.61163459578529e-05</v>
       </c>
       <c r="CG15" t="n">
-        <v>8.778316987445578e-05</v>
+        <v>0.002067075576633215</v>
       </c>
       <c r="CH15" t="n">
-        <v>5.037145820097066e-05</v>
+        <v>0.0002426754217594862</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.628284164529759e-06</v>
+        <v>0.002367845736443996</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.758344453468453e-05</v>
+        <v>2.237051376141608e-05</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.210764730785741e-05</v>
+        <v>0.0005129748024046421</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.865256490418687e-05</v>
+        <v>0.001095582963898778</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0002451503823976964</v>
+        <v>0.0001716430415399373</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0001330024970229715</v>
+        <v>0.0005045714206062257</v>
       </c>
       <c r="CO15" t="n">
-        <v>2.543839218560606e-05</v>
+        <v>0.002867648145183921</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0001797659060684964</v>
+        <v>0.002074587158858776</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0001986244751606137</v>
+        <v>0.003257209900766611</v>
       </c>
       <c r="CR15" t="n">
-        <v>8.762424840824679e-05</v>
+        <v>0.0009218968916684389</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0001025521123665385</v>
+        <v>0.0005358793423511088</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0001970319863175973</v>
+        <v>0.0006762837874703109</v>
       </c>
       <c r="CU15" t="n">
-        <v>6.278410182858352e-06</v>
+        <v>0.0007428426761180162</v>
       </c>
       <c r="CV15" t="n">
-        <v>7.947517588036135e-06</v>
+        <v>0.0003439023275859654</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0002094082883559167</v>
+        <v>0.001969421748071909</v>
       </c>
       <c r="CX15" t="n">
-        <v>8.124487794702873e-05</v>
+        <v>0.0002467101148795336</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0001181604893645272</v>
+        <v>0.002285072114318609</v>
       </c>
       <c r="CZ15" t="n">
-        <v>5.459087697090581e-05</v>
+        <v>0.0005040469695813954</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.426704122626688e-05</v>
+        <v>0.002502718241885304</v>
       </c>
       <c r="DB15" t="n">
-        <v>3.048015605600085e-05</v>
+        <v>0.0002044757129624486</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07816392503446e-05</v>
+        <v>0.000410553504480049</v>
       </c>
       <c r="DD15" t="n">
-        <v>5.655311724694911e-06</v>
+        <v>0.0007739789434708655</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0001391454425174743</v>
+        <v>0.0004011738346889615</v>
       </c>
       <c r="DF15" t="n">
-        <v>4.260542482370511e-05</v>
+        <v>0.001808445900678635</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.133553011342883e-05</v>
+        <v>0.002614437602460384</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.000213533901842311</v>
+        <v>0.0009232634329237044</v>
       </c>
       <c r="DI15" t="n">
-        <v>5.458637315314263e-05</v>
+        <v>0.001593678258359432</v>
       </c>
       <c r="DJ15" t="n">
-        <v>9.841154678724706e-06</v>
+        <v>0.00248977611772716</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.336417648824863e-06</v>
+        <v>0.0002860409731511027</v>
       </c>
       <c r="DL15" t="n">
-        <v>7.405684300465509e-05</v>
+        <v>0.001663260278292</v>
       </c>
       <c r="DM15" t="n">
-        <v>5.503986903931946e-05</v>
+        <v>0.001266476465389132</v>
       </c>
       <c r="DN15" t="n">
-        <v>3.288207881269045e-05</v>
+        <v>0.0008136248216032982</v>
       </c>
       <c r="DO15" t="n">
-        <v>5.450794560601935e-05</v>
+        <v>0.002140191849321127</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.370215073227882e-05</v>
+        <v>0.00128638930618763</v>
       </c>
       <c r="DQ15" t="n">
-        <v>4.914311648462899e-05</v>
+        <v>0.001307280035689473</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0001187483430840075</v>
+        <v>0.0002146101032849401</v>
       </c>
       <c r="DS15" t="n">
-        <v>1.548311593069229e-05</v>
+        <v>0.0009489060612395406</v>
       </c>
       <c r="DT15" t="n">
-        <v>3.700768138514832e-05</v>
+        <v>0.001088219694793224</v>
       </c>
       <c r="DU15" t="n">
-        <v>3.931271567125805e-05</v>
+        <v>0.00187591603025794</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.714667349820957e-05</v>
+        <v>0.001636137720197439</v>
       </c>
       <c r="DW15" t="n">
-        <v>5.510651317308657e-05</v>
+        <v>0.0006125220097601414</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0001728328206809238</v>
+        <v>0.000900211394764483</v>
       </c>
       <c r="DY15" t="n">
-        <v>4.485156750888564e-06</v>
+        <v>0.001481007668189704</v>
       </c>
       <c r="DZ15" t="n">
-        <v>7.930225547170267e-05</v>
+        <v>0.0005635982379317284</v>
       </c>
       <c r="EA15" t="n">
-        <v>8.215229900088161e-05</v>
+        <v>0.0007189686875790358</v>
       </c>
       <c r="EB15" t="n">
-        <v>4.11438086302951e-05</v>
+        <v>0.0006004640599712729</v>
       </c>
       <c r="EC15" t="n">
-        <v>5.013807458453812e-05</v>
+        <v>0.0004912091535516083</v>
       </c>
       <c r="ED15" t="n">
-        <v>3.238062345189974e-05</v>
+        <v>0.002290863776579499</v>
       </c>
       <c r="EE15" t="n">
-        <v>1.787780274753459e-05</v>
+        <v>0.001957651926204562</v>
       </c>
       <c r="EF15" t="n">
-        <v>1.017374597722664e-05</v>
+        <v>7.645630103070289e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0001916957553476095</v>
+        <v>0.001619418384507298</v>
       </c>
       <c r="EH15" t="n">
-        <v>8.545852324459702e-05</v>
+        <v>0.001449144328944385</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0001491655712015927</v>
+        <v>0.001117801177315414</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0001380762550979853</v>
+        <v>0.001073490595445037</v>
       </c>
       <c r="EK15" t="n">
-        <v>4.005398295703344e-06</v>
+        <v>0.002052785130217671</v>
       </c>
       <c r="EL15" t="n">
-        <v>2.095560557791032e-05</v>
+        <v>0.0004391200200188905</v>
       </c>
       <c r="EM15" t="n">
-        <v>3.199244747520424e-05</v>
+        <v>0.0008773732115514576</v>
       </c>
       <c r="EN15" t="n">
-        <v>1.641512972128112e-05</v>
+        <v>0.0005498949903994799</v>
       </c>
       <c r="EO15" t="n">
-        <v>7.316655683098361e-06</v>
+        <v>0.0007421124028041959</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0002431073226034641</v>
+        <v>0.001663394388742745</v>
       </c>
       <c r="EQ15" t="n">
-        <v>8.969190093921497e-05</v>
+        <v>0.0009446869371458888</v>
       </c>
       <c r="ER15" t="n">
-        <v>5.141478322912008e-05</v>
+        <v>0.002209713216871023</v>
       </c>
       <c r="ES15" t="n">
-        <v>3.195879253325984e-05</v>
+        <v>0.001066897995769978</v>
       </c>
       <c r="ET15" t="n">
-        <v>1.931770020746626e-05</v>
+        <v>0.0001642657734919339</v>
       </c>
       <c r="EU15" t="n">
-        <v>6.526082142954692e-05</v>
+        <v>0.0004400578327476978</v>
       </c>
       <c r="EV15" t="n">
-        <v>1.792196417227387e-05</v>
+        <v>0.0006878377171233296</v>
       </c>
       <c r="EW15" t="n">
-        <v>4.453399014892057e-05</v>
+        <v>0.00162464112509042</v>
       </c>
       <c r="EX15" t="n">
-        <v>3.679354631458409e-05</v>
+        <v>0.0003025837359018624</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0002170478401239961</v>
+        <v>0.002520188223570585</v>
       </c>
       <c r="EZ15" t="n">
-        <v>4.544567127595656e-05</v>
+        <v>3.604738594731316e-05</v>
       </c>
       <c r="FA15" t="n">
-        <v>9.703264367999509e-05</v>
+        <v>0.002418260555714369</v>
       </c>
       <c r="FB15" t="n">
-        <v>3.322424890939146e-05</v>
+        <v>0.0001109361037379131</v>
       </c>
       <c r="FC15" t="n">
-        <v>2.489359576429706e-05</v>
+        <v>0.002173896413296461</v>
       </c>
       <c r="FD15" t="n">
-        <v>2.113794835167937e-05</v>
+        <v>1.076870830729604e-06</v>
       </c>
       <c r="FE15" t="n">
-        <v>1.768958100001328e-06</v>
+        <v>0.0004513089661486447</v>
       </c>
       <c r="FF15" t="n">
-        <v>1.292607157665771e-05</v>
+        <v>0.0004487551341298968</v>
       </c>
       <c r="FG15" t="n">
-        <v>3.751036638277583e-05</v>
+        <v>0.0001382965128868818</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.000140382515382953</v>
+        <v>0.001197111210785806</v>
       </c>
       <c r="FI15" t="n">
-        <v>7.408091187244281e-05</v>
+        <v>0.002588902832940221</v>
       </c>
       <c r="FJ15" t="n">
-        <v>5.688206510967575e-05</v>
+        <v>0.002074936404824257</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001003846264211461</v>
+        <v>0.0005882225232198834</v>
       </c>
       <c r="FL15" t="n">
-        <v>4.422290294314735e-05</v>
+        <v>0.002624577842652798</v>
       </c>
       <c r="FM15" t="n">
-        <v>6.233585008885711e-05</v>
+        <v>0.0001111890451284125</v>
       </c>
       <c r="FN15" t="n">
-        <v>5.101818169350736e-05</v>
+        <v>0.001809860463254154</v>
       </c>
       <c r="FO15" t="n">
-        <v>1.310609877691604e-05</v>
+        <v>0.002066230634227395</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001237559772562236</v>
+        <v>0.0009102160693146288</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0001290381042053923</v>
+        <v>0.0003839939599856734</v>
       </c>
       <c r="FR15" t="n">
-        <v>9.953112021321431e-05</v>
+        <v>0.004291885066777468</v>
       </c>
       <c r="FS15" t="n">
-        <v>6.117014709161595e-05</v>
+        <v>0.0001065130127244629</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0001062958617694676</v>
+        <v>0.0009037568233907223</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0001173694327007979</v>
+        <v>0.001121725421398878</v>
       </c>
       <c r="FV15" t="n">
-        <v>3.559636388672516e-05</v>
+        <v>0.00056970224250108</v>
       </c>
       <c r="FW15" t="n">
-        <v>6.148120883153751e-05</v>
+        <v>0.001715675345622003</v>
       </c>
       <c r="FX15" t="n">
-        <v>3.437186751398258e-05</v>
+        <v>0.001949927071109414</v>
       </c>
       <c r="FY15" t="n">
-        <v>8.293368591694161e-05</v>
+        <v>0.0006910819793120027</v>
       </c>
       <c r="FZ15" t="n">
-        <v>5.901184340473264e-05</v>
+        <v>0.001687851967290044</v>
       </c>
       <c r="GA15" t="n">
-        <v>3.358396497787908e-05</v>
+        <v>0.002377742901444435</v>
       </c>
       <c r="GB15" t="n">
-        <v>5.542150029214099e-05</v>
+        <v>0.0006850589998066425</v>
       </c>
       <c r="GC15" t="n">
-        <v>3.633194137364626e-05</v>
+        <v>0.004138852935284376</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0001386779767926782</v>
+        <v>0.00383151788264513</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0001559835800435394</v>
+        <v>0.0007437053136527538</v>
       </c>
       <c r="GF15" t="n">
-        <v>5.881403922103345e-05</v>
+        <v>0.0002825551782734692</v>
       </c>
       <c r="GG15" t="n">
-        <v>9.901988232741132e-05</v>
+        <v>0.0004257845575921237</v>
       </c>
     </row>
     <row r="16">
@@ -9534,571 +9534,571 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.550500201119576e-05</v>
+        <v>0.05168557912111282</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0005127161275595427</v>
+        <v>0.6011913418769836</v>
       </c>
       <c r="C17" t="n">
-        <v>6.337924787658267e-06</v>
+        <v>0.02656630240380764</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001516618358436972</v>
+        <v>0.1775253415107727</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0001039557319018058</v>
+        <v>0.1990625411272049</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002040562249021605</v>
+        <v>0.009934328496456146</v>
       </c>
       <c r="G17" t="n">
-        <v>5.863129990757443e-05</v>
+        <v>0.04839101806282997</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0001654067600611597</v>
+        <v>0.08680093288421631</v>
       </c>
       <c r="I17" t="n">
-        <v>7.21042015356943e-05</v>
+        <v>0.07341671735048294</v>
       </c>
       <c r="J17" t="n">
-        <v>8.453101327177137e-05</v>
+        <v>0.02415493130683899</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000461853458546102</v>
+        <v>0.7532019019126892</v>
       </c>
       <c r="L17" t="n">
-        <v>4.308296047383919e-05</v>
+        <v>0.06872817128896713</v>
       </c>
       <c r="M17" t="n">
-        <v>5.423289985628799e-05</v>
+        <v>0.2973628640174866</v>
       </c>
       <c r="N17" t="n">
-        <v>5.222506842983421e-06</v>
+        <v>0.004954829812049866</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0002077783283311874</v>
+        <v>0.01980531215667725</v>
       </c>
       <c r="P17" t="n">
-        <v>8.164947212208062e-05</v>
+        <v>0.0001979470252990723</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.28352858661674e-06</v>
+        <v>0.1379066854715347</v>
       </c>
       <c r="R17" t="n">
-        <v>9.726442658575252e-05</v>
+        <v>0.06884324550628662</v>
       </c>
       <c r="S17" t="n">
-        <v>1.385243649565382e-05</v>
+        <v>0.03502894565463066</v>
       </c>
       <c r="T17" t="n">
-        <v>4.34410831076093e-05</v>
+        <v>0.09738644957542419</v>
       </c>
       <c r="U17" t="n">
-        <v>3.263719554524869e-05</v>
+        <v>0.05015347525477409</v>
       </c>
       <c r="V17" t="n">
-        <v>5.444062844617292e-05</v>
+        <v>0.08904401957988739</v>
       </c>
       <c r="W17" t="n">
-        <v>7.546448614448309e-05</v>
+        <v>0.07238367944955826</v>
       </c>
       <c r="X17" t="n">
-        <v>4.873979196418077e-05</v>
+        <v>0.01762713119387627</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.223785461159423e-05</v>
+        <v>0.0786491259932518</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.479009218513966e-05</v>
+        <v>0.1703144162893295</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.217615398578346e-05</v>
+        <v>0.02993478253483772</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85219178092666e-05</v>
+        <v>0.00294961966574192</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.864547968783882e-05</v>
+        <v>0.0195755623281002</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.46150331501849e-05</v>
+        <v>0.1255358159542084</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.137517301685875e-05</v>
+        <v>0.2178937196731567</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.098430897807702e-05</v>
+        <v>0.1654509305953979</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.695594386954326e-06</v>
+        <v>0.02598021924495697</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.238929326063953e-05</v>
+        <v>0.02498956955969334</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.594977483269759e-05</v>
+        <v>0.1668076813220978</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.823877705144696e-06</v>
+        <v>0.06619276106357574</v>
       </c>
       <c r="AK17" t="n">
-        <v>6.711645983159542e-05</v>
+        <v>0.1000049859285355</v>
       </c>
       <c r="AL17" t="n">
-        <v>7.233830547193065e-05</v>
+        <v>0.09627345949411392</v>
       </c>
       <c r="AM17" t="n">
-        <v>8.763240657572169e-07</v>
+        <v>0.08127546310424805</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.026990088983439e-05</v>
+        <v>0.06841091066598892</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.790449101070408e-06</v>
+        <v>0.01305397227406502</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.780272426316515e-05</v>
+        <v>0.004937093704938889</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.534564893925563e-05</v>
+        <v>0.09206630289554596</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.308145824121311e-05</v>
+        <v>0.1968380212783813</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.850791421835311e-05</v>
+        <v>0.03878490999341011</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.11060068977531e-06</v>
+        <v>0.1813680529594421</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0003038653521798551</v>
+        <v>0.5042177438735962</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.091091952635907e-05</v>
+        <v>0.07868832349777222</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.984075712854974e-05</v>
+        <v>0.2220492362976074</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.034021498635411e-05</v>
+        <v>0.2516067028045654</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0001337895228061825</v>
+        <v>0.0773124098777771</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0001140639142249711</v>
+        <v>0.02784054167568684</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.366867016069591e-05</v>
+        <v>0.06191462278366089</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.217942715622485e-05</v>
+        <v>0.07321999967098236</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.515677912626415e-06</v>
+        <v>0.1418801993131638</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0001148059964179993</v>
+        <v>0.0328940711915493</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.000111396650027018</v>
+        <v>0.05965974554419518</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.098389035789296e-05</v>
+        <v>0.02031303942203522</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.821465750457719e-05</v>
+        <v>0.06623611599206924</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.131209763931111e-05</v>
+        <v>0.03050932660698891</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.04457314289175e-05</v>
+        <v>0.18305703997612</v>
       </c>
       <c r="BJ17" t="n">
-        <v>7.937414920888841e-05</v>
+        <v>0.1694552898406982</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.564881186932325e-05</v>
+        <v>0.08052337914705276</v>
       </c>
       <c r="BL17" t="n">
-        <v>2.923755710071418e-05</v>
+        <v>0.06252489984035492</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.302226418280043e-05</v>
+        <v>0.04824116080999374</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.144297392689623e-05</v>
+        <v>0.04894037544727325</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.097095057251863e-05</v>
+        <v>0.0699533224105835</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.34138097363757e-06</v>
+        <v>0.1600662022829056</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.747930557234213e-05</v>
+        <v>0.0002505570009816438</v>
       </c>
       <c r="BR17" t="n">
-        <v>6.072054384276271e-05</v>
+        <v>0.1828694939613342</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.359173595323227e-05</v>
+        <v>0.07555840164422989</v>
       </c>
       <c r="BT17" t="n">
-        <v>1.286608494410757e-05</v>
+        <v>0.12154620885849</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.478342816582881e-06</v>
+        <v>0.08741423487663269</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.0001835147850215435</v>
+        <v>0.3046643137931824</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.831232167314738e-05</v>
+        <v>0.09792131185531616</v>
       </c>
       <c r="BX17" t="n">
-        <v>4.874527803622186e-06</v>
+        <v>0.1002838611602783</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.175885260337964e-05</v>
+        <v>0.02649367228150368</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.938156027696095e-05</v>
+        <v>0.002091461792588234</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.064586391905323e-07</v>
+        <v>0.1288148015737534</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.380634941800963e-05</v>
+        <v>0.06010345369577408</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.062912871129811e-05</v>
+        <v>0.03837532922625542</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.333895049057901e-06</v>
+        <v>0.0134234856814146</v>
       </c>
       <c r="CE17" t="n">
-        <v>9.143551869783551e-05</v>
+        <v>0.1918596476316452</v>
       </c>
       <c r="CF17" t="n">
-        <v>4.460943819140084e-05</v>
+        <v>0.01709822192788124</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.722478348005097e-05</v>
+        <v>0.0236321147531271</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.5124591300264e-05</v>
+        <v>0.01950725913047791</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.248045191459823e-05</v>
+        <v>0.01868217810988426</v>
       </c>
       <c r="CJ17" t="n">
-        <v>3.460405423538759e-05</v>
+        <v>0.02357287704944611</v>
       </c>
       <c r="CK17" t="n">
-        <v>2.234468774986453e-05</v>
+        <v>0.03947960957884789</v>
       </c>
       <c r="CL17" t="n">
-        <v>4.904501838609576e-05</v>
+        <v>0.007615658454596996</v>
       </c>
       <c r="CM17" t="n">
-        <v>6.316610233625397e-05</v>
+        <v>0.02533257938921452</v>
       </c>
       <c r="CN17" t="n">
-        <v>5.410677840700373e-05</v>
+        <v>0.1418206244707108</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.369095298286993e-05</v>
+        <v>0.06863545626401901</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0001347056968370453</v>
+        <v>0.1206311583518982</v>
       </c>
       <c r="CQ17" t="n">
-        <v>6.840496644144878e-05</v>
+        <v>0.124967947602272</v>
       </c>
       <c r="CR17" t="n">
-        <v>6.915810809005052e-05</v>
+        <v>0.01928186044096947</v>
       </c>
       <c r="CS17" t="n">
-        <v>9.991737169912085e-05</v>
+        <v>0.1441674530506134</v>
       </c>
       <c r="CT17" t="n">
-        <v>6.914306140970439e-05</v>
+        <v>0.08244511485099792</v>
       </c>
       <c r="CU17" t="n">
-        <v>3.706922143464908e-05</v>
+        <v>0.04664375633001328</v>
       </c>
       <c r="CV17" t="n">
-        <v>4.805613116332097e-06</v>
+        <v>0.03250417858362198</v>
       </c>
       <c r="CW17" t="n">
-        <v>8.137537952279672e-05</v>
+        <v>0.1771021485328674</v>
       </c>
       <c r="CX17" t="n">
-        <v>4.979349614586681e-05</v>
+        <v>0.02907192148268223</v>
       </c>
       <c r="CY17" t="n">
-        <v>5.326647806214169e-05</v>
+        <v>0.06658336520195007</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.218765075667761e-05</v>
+        <v>0.05906595289707184</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.267427796847187e-05</v>
+        <v>0.03125095367431641</v>
       </c>
       <c r="DB17" t="n">
-        <v>3.727547300513834e-05</v>
+        <v>6.125494837760925e-05</v>
       </c>
       <c r="DC17" t="n">
-        <v>4.259499837644398e-05</v>
+        <v>0.03564213588833809</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.313770841690712e-05</v>
+        <v>0.02171437814831734</v>
       </c>
       <c r="DE17" t="n">
-        <v>4.709084532805718e-05</v>
+        <v>0.02150282263755798</v>
       </c>
       <c r="DF17" t="n">
-        <v>8.267715747933835e-05</v>
+        <v>0.04203056544065475</v>
       </c>
       <c r="DG17" t="n">
-        <v>5.540507117984816e-06</v>
+        <v>0.02972458675503731</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0002361258084420115</v>
+        <v>0.09615409374237061</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0001252373185707256</v>
+        <v>0.3227706849575043</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0001785626373020932</v>
+        <v>0.06977637112140656</v>
       </c>
       <c r="DK17" t="n">
-        <v>7.847024244256318e-05</v>
+        <v>0.03392781317234039</v>
       </c>
       <c r="DL17" t="n">
-        <v>8.302400965476409e-05</v>
+        <v>0.113826647400856</v>
       </c>
       <c r="DM17" t="n">
-        <v>7.895268936408684e-05</v>
+        <v>0.1813711225986481</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.19997873500688e-05</v>
+        <v>0.0459730327129364</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.492371615720913e-05</v>
+        <v>0.02441104501485825</v>
       </c>
       <c r="DP17" t="n">
-        <v>4.08498672186397e-05</v>
+        <v>0.02043340913951397</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.452378364774631e-05</v>
+        <v>0.05504104495048523</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.696282409597188e-06</v>
+        <v>0.119002491235733</v>
       </c>
       <c r="DS17" t="n">
-        <v>3.262631798861548e-05</v>
+        <v>0.06268221139907837</v>
       </c>
       <c r="DT17" t="n">
-        <v>4.44957877334673e-05</v>
+        <v>0.1785934269428253</v>
       </c>
       <c r="DU17" t="n">
-        <v>2.893889723054599e-05</v>
+        <v>0.02135967835783958</v>
       </c>
       <c r="DV17" t="n">
-        <v>2.481209412508179e-05</v>
+        <v>0.1387789696455002</v>
       </c>
       <c r="DW17" t="n">
-        <v>1.562979196023662e-05</v>
+        <v>0.07930327206850052</v>
       </c>
       <c r="DX17" t="n">
-        <v>2.909154864028096e-05</v>
+        <v>0.02729667723178864</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.810468428535387e-05</v>
+        <v>0.005595753435045481</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.435821054154076e-05</v>
+        <v>0.06998182088136673</v>
       </c>
       <c r="EA17" t="n">
-        <v>5.356703695724718e-06</v>
+        <v>0.006653457880020142</v>
       </c>
       <c r="EB17" t="n">
-        <v>3.168445618939586e-05</v>
+        <v>0.04270472377538681</v>
       </c>
       <c r="EC17" t="n">
-        <v>6.247513738344423e-06</v>
+        <v>0.04377730563282967</v>
       </c>
       <c r="ED17" t="n">
-        <v>2.282685454702005e-05</v>
+        <v>0.1910985261201859</v>
       </c>
       <c r="EE17" t="n">
-        <v>7.910808926681057e-05</v>
+        <v>0.1488259434700012</v>
       </c>
       <c r="EF17" t="n">
-        <v>2.399622280790936e-05</v>
+        <v>0.05794965103268623</v>
       </c>
       <c r="EG17" t="n">
-        <v>9.34709096327424e-05</v>
+        <v>0.1182228401303291</v>
       </c>
       <c r="EH17" t="n">
-        <v>1.443707515136339e-05</v>
+        <v>0.05707023665308952</v>
       </c>
       <c r="EI17" t="n">
-        <v>1.873192377388477e-05</v>
+        <v>0.0268856305629015</v>
       </c>
       <c r="EJ17" t="n">
-        <v>6.345194560708478e-05</v>
+        <v>0.06065090000629425</v>
       </c>
       <c r="EK17" t="n">
-        <v>3.368274337844923e-05</v>
+        <v>0.03226448595523834</v>
       </c>
       <c r="EL17" t="n">
-        <v>4.337088466854766e-05</v>
+        <v>0.04213003814220428</v>
       </c>
       <c r="EM17" t="n">
-        <v>3.571959496184718e-06</v>
+        <v>0.07599250227212906</v>
       </c>
       <c r="EN17" t="n">
-        <v>2.315322490176186e-05</v>
+        <v>0.04835078120231628</v>
       </c>
       <c r="EO17" t="n">
-        <v>1.101165253203362e-06</v>
+        <v>0.07180389016866684</v>
       </c>
       <c r="EP17" t="n">
-        <v>5.238272569840774e-05</v>
+        <v>0.09043675661087036</v>
       </c>
       <c r="EQ17" t="n">
-        <v>9.8613221780397e-05</v>
+        <v>0.005965039134025574</v>
       </c>
       <c r="ER17" t="n">
-        <v>9.846196189755574e-05</v>
+        <v>0.01951106265187263</v>
       </c>
       <c r="ES17" t="n">
-        <v>6.801622657803819e-05</v>
+        <v>0.0918264165520668</v>
       </c>
       <c r="ET17" t="n">
-        <v>2.138650415872689e-05</v>
+        <v>0.0007307045161724091</v>
       </c>
       <c r="EU17" t="n">
-        <v>9.631617285776883e-05</v>
+        <v>0.01781386509537697</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0001037563342833892</v>
+        <v>0.05448741093277931</v>
       </c>
       <c r="EW17" t="n">
-        <v>7.995271516847424e-06</v>
+        <v>0.003652847371995449</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.623555817786837e-06</v>
+        <v>0.0009272657334804535</v>
       </c>
       <c r="EY17" t="n">
-        <v>7.884585647843778e-05</v>
+        <v>0.2062731832265854</v>
       </c>
       <c r="EZ17" t="n">
-        <v>3.979816028731875e-05</v>
+        <v>0.02065153233706951</v>
       </c>
       <c r="FA17" t="n">
-        <v>1.582194636284839e-05</v>
+        <v>0.0482037253677845</v>
       </c>
       <c r="FB17" t="n">
-        <v>3.052682586712763e-05</v>
+        <v>0.08056836575269699</v>
       </c>
       <c r="FC17" t="n">
-        <v>1.422074547008378e-05</v>
+        <v>0.01647572964429855</v>
       </c>
       <c r="FD17" t="n">
-        <v>6.408242916222662e-05</v>
+        <v>0.02763139829039574</v>
       </c>
       <c r="FE17" t="n">
-        <v>4.306792834540829e-05</v>
+        <v>0.03475558012723923</v>
       </c>
       <c r="FF17" t="n">
-        <v>5.967739707557485e-05</v>
+        <v>0.03393106162548065</v>
       </c>
       <c r="FG17" t="n">
-        <v>2.351411603740416e-05</v>
+        <v>0.03011824935674667</v>
       </c>
       <c r="FH17" t="n">
-        <v>1.828174845286412e-06</v>
+        <v>0.2264510691165924</v>
       </c>
       <c r="FI17" t="n">
-        <v>8.790862193563953e-05</v>
+        <v>0.01859267055988312</v>
       </c>
       <c r="FJ17" t="n">
-        <v>4.875326339970343e-05</v>
+        <v>0.1553203463554382</v>
       </c>
       <c r="FK17" t="n">
-        <v>1.437653918401338e-05</v>
+        <v>0.05266086012125015</v>
       </c>
       <c r="FL17" t="n">
-        <v>1.69077429745812e-05</v>
+        <v>0.07480037957429886</v>
       </c>
       <c r="FM17" t="n">
-        <v>4.077191624674015e-05</v>
+        <v>0.1669122278690338</v>
       </c>
       <c r="FN17" t="n">
-        <v>3.293580812169239e-05</v>
+        <v>0.07369296252727509</v>
       </c>
       <c r="FO17" t="n">
-        <v>4.139136945013888e-05</v>
+        <v>0.01179663091897964</v>
       </c>
       <c r="FP17" t="n">
-        <v>4.008326504845172e-05</v>
+        <v>0.09809864312410355</v>
       </c>
       <c r="FQ17" t="n">
-        <v>2.855907223420218e-05</v>
+        <v>0.1236151307821274</v>
       </c>
       <c r="FR17" t="n">
-        <v>7.860719779273495e-05</v>
+        <v>0.04526906460523605</v>
       </c>
       <c r="FS17" t="n">
-        <v>8.9776556706056e-05</v>
+        <v>0.01268695667386055</v>
       </c>
       <c r="FT17" t="n">
-        <v>7.26435609976761e-05</v>
+        <v>0.268320620059967</v>
       </c>
       <c r="FU17" t="n">
-        <v>3.845117316814139e-05</v>
+        <v>0.4108781218528748</v>
       </c>
       <c r="FV17" t="n">
-        <v>7.942298543639481e-05</v>
+        <v>0.08670045435428619</v>
       </c>
       <c r="FW17" t="n">
-        <v>3.632399966591038e-06</v>
+        <v>0.03294956311583519</v>
       </c>
       <c r="FX17" t="n">
-        <v>3.311339241918176e-05</v>
+        <v>0.008155852556228638</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0001021419302560389</v>
+        <v>0.1298279017210007</v>
       </c>
       <c r="FZ17" t="n">
-        <v>2.034310637100134e-05</v>
+        <v>0.007652627304196358</v>
       </c>
       <c r="GA17" t="n">
-        <v>5.030962347518653e-05</v>
+        <v>0.08649618178606033</v>
       </c>
       <c r="GB17" t="n">
-        <v>3.197345722583123e-05</v>
+        <v>0.003020565956830978</v>
       </c>
       <c r="GC17" t="n">
-        <v>2.05206852115225e-05</v>
+        <v>0.08036941289901733</v>
       </c>
       <c r="GD17" t="n">
-        <v>5.581208097282797e-05</v>
+        <v>0.01473275944590569</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.0001436285092495382</v>
+        <v>0.1221966445446014</v>
       </c>
       <c r="GF17" t="n">
-        <v>1.074353531294037e-05</v>
+        <v>0.003127872943878174</v>
       </c>
       <c r="GG17" t="n">
-        <v>1.246677766175708e-05</v>
+        <v>0.0824502632021904</v>
       </c>
     </row>
   </sheetData>
